--- a/research/traditional_assets/database/data/philippines/philippines_utility_water.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_utility_water.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07496697893825907</v>
+        <v>0.07481331149091343</v>
       </c>
       <c r="C2">
-        <v>3217.795879199722</v>
+        <v>3190.234636572576</v>
       </c>
       <c r="D2">
-        <v>3065.295879199722</v>
+        <v>3069.929636572576</v>
       </c>
       <c r="E2">
-        <v>-1846.5</v>
+        <v>-1814.305</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.195</v>
       </c>
       <c r="G2">
         <v>152.5</v>
@@ -1457,28 +1457,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6194085</v>
       </c>
       <c r="N2">
-        <v>346.3530612244898</v>
+        <v>344.7336527244898</v>
       </c>
       <c r="O2">
-        <v>86.58826530612245</v>
+        <v>86.18341318112245</v>
       </c>
       <c r="P2">
-        <v>259.7647959183673</v>
+        <v>258.5502395433674</v>
       </c>
       <c r="Q2">
-        <v>346.0647959183673</v>
+        <v>344.8502395433674</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07496697893825907</v>
+        <v>0.07518794089991256</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.4276303482106447</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>213.8762771866949</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07481331149091343</v>
+        <v>0.0746596440435678</v>
       </c>
       <c r="C3">
-        <v>3190.234636572576</v>
+        <v>3162.687424705137</v>
       </c>
       <c r="D3">
-        <v>3069.929636572576</v>
+        <v>3074.577424705137</v>
       </c>
       <c r="E3">
-        <v>-1814.305</v>
+        <v>-1782.11</v>
       </c>
       <c r="F3">
-        <v>32.195</v>
+        <v>64.39</v>
       </c>
       <c r="G3">
         <v>152.5</v>
@@ -1539,28 +1539,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M3">
-        <v>1.6194085</v>
+        <v>3.238817</v>
       </c>
       <c r="N3">
-        <v>344.7336527244898</v>
+        <v>343.1142442244898</v>
       </c>
       <c r="O3">
-        <v>86.18341318112245</v>
+        <v>85.77856105612246</v>
       </c>
       <c r="P3">
-        <v>258.5502395433674</v>
+        <v>257.3356831683674</v>
       </c>
       <c r="Q3">
-        <v>344.8502395433674</v>
+        <v>343.6356831683674</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07518794089991256</v>
+        <v>0.07541341228935489</v>
       </c>
       <c r="T3">
-        <v>0.4276303482106447</v>
+        <v>0.4309112316555629</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>213.8762771866949</v>
+        <v>106.9381385933474</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0746596440435678</v>
+        <v>0.07450597659622213</v>
       </c>
       <c r="C4">
-        <v>3162.687424705137</v>
+        <v>3135.154307420576</v>
       </c>
       <c r="D4">
-        <v>3074.577424705137</v>
+        <v>3079.239307420576</v>
       </c>
       <c r="E4">
-        <v>-1782.11</v>
+        <v>-1749.915</v>
       </c>
       <c r="F4">
-        <v>64.39</v>
+        <v>96.58499999999999</v>
       </c>
       <c r="G4">
         <v>152.5</v>
@@ -1621,28 +1621,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M4">
-        <v>3.238817</v>
+        <v>4.8582255</v>
       </c>
       <c r="N4">
-        <v>343.1142442244898</v>
+        <v>341.4948357244898</v>
       </c>
       <c r="O4">
-        <v>85.77856105612246</v>
+        <v>85.37370893112245</v>
       </c>
       <c r="P4">
-        <v>257.3356831683674</v>
+        <v>256.1211267933674</v>
       </c>
       <c r="Q4">
-        <v>343.6356831683674</v>
+        <v>342.4211267933674</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07541341228935489</v>
+        <v>0.07564353257342488</v>
       </c>
       <c r="T4">
-        <v>0.4309112316555629</v>
+        <v>0.4342597621818197</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.9381385933474</v>
+        <v>71.29209239556496</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07450597659622213</v>
+        <v>0.07435230914887649</v>
       </c>
       <c r="C5">
-        <v>3135.154307420576</v>
+        <v>3107.635348929736</v>
       </c>
       <c r="D5">
-        <v>3079.239307420576</v>
+        <v>3083.915348929736</v>
       </c>
       <c r="E5">
-        <v>-1749.915</v>
+        <v>-1717.72</v>
       </c>
       <c r="F5">
-        <v>96.58499999999999</v>
+        <v>128.78</v>
       </c>
       <c r="G5">
         <v>152.5</v>
@@ -1703,28 +1703,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M5">
-        <v>4.8582255</v>
+        <v>6.477634</v>
       </c>
       <c r="N5">
-        <v>341.4948357244898</v>
+        <v>339.8754272244898</v>
       </c>
       <c r="O5">
-        <v>85.37370893112245</v>
+        <v>84.96885680612245</v>
       </c>
       <c r="P5">
-        <v>256.1211267933674</v>
+        <v>254.9065704183673</v>
       </c>
       <c r="Q5">
-        <v>342.4211267933674</v>
+        <v>341.2065704183673</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07564353257342488</v>
+        <v>0.07587844703007968</v>
       </c>
       <c r="T5">
-        <v>0.4342597621818197</v>
+        <v>0.4376780537607068</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>71.29209239556496</v>
+        <v>53.46906929667372</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07435230914887649</v>
+        <v>0.07419864170153083</v>
       </c>
       <c r="C6">
-        <v>3107.635348929736</v>
+        <v>3080.130613834095</v>
       </c>
       <c r="D6">
-        <v>3083.915348929736</v>
+        <v>3088.605613834095</v>
       </c>
       <c r="E6">
-        <v>-1717.72</v>
+        <v>-1685.525</v>
       </c>
       <c r="F6">
-        <v>128.78</v>
+        <v>160.975</v>
       </c>
       <c r="G6">
         <v>152.5</v>
@@ -1785,28 +1785,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M6">
-        <v>6.477634</v>
+        <v>8.097042500000001</v>
       </c>
       <c r="N6">
-        <v>339.8754272244898</v>
+        <v>338.2560187244898</v>
       </c>
       <c r="O6">
-        <v>84.96885680612245</v>
+        <v>84.56400468112246</v>
       </c>
       <c r="P6">
-        <v>254.9065704183673</v>
+        <v>253.6920140433674</v>
       </c>
       <c r="Q6">
-        <v>341.2065704183673</v>
+        <v>339.9920140433674</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07587844703007968</v>
+        <v>0.07611830705424298</v>
       </c>
       <c r="T6">
-        <v>0.4376780537607068</v>
+        <v>0.4411683093728336</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.46906929667372</v>
+        <v>42.77525543733898</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07419864170153083</v>
+        <v>0.07404497425418519</v>
       </c>
       <c r="C7">
-        <v>3080.130613834095</v>
+        <v>3052.640167128728</v>
       </c>
       <c r="D7">
-        <v>3088.605613834095</v>
+        <v>3093.310167128728</v>
       </c>
       <c r="E7">
-        <v>-1685.525</v>
+        <v>-1653.33</v>
       </c>
       <c r="F7">
-        <v>160.975</v>
+        <v>193.17</v>
       </c>
       <c r="G7">
         <v>152.5</v>
@@ -1867,28 +1867,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M7">
-        <v>8.097042500000001</v>
+        <v>9.716451000000001</v>
       </c>
       <c r="N7">
-        <v>338.2560187244898</v>
+        <v>336.6366102244898</v>
       </c>
       <c r="O7">
-        <v>84.56400468112246</v>
+        <v>84.15915255612245</v>
       </c>
       <c r="P7">
-        <v>253.6920140433674</v>
+        <v>252.4774576683674</v>
       </c>
       <c r="Q7">
-        <v>339.9920140433674</v>
+        <v>338.7774576683673</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07611830705424298</v>
+        <v>0.07636327048317573</v>
       </c>
       <c r="T7">
-        <v>0.4411683093728336</v>
+        <v>0.4447328257426653</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.77525543733898</v>
+        <v>35.64604619778248</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07404497425418519</v>
+        <v>0.07389130680683954</v>
       </c>
       <c r="C8">
-        <v>3052.640167128728</v>
+        <v>3025.16407420532</v>
       </c>
       <c r="D8">
-        <v>3093.310167128728</v>
+        <v>3098.029074205319</v>
       </c>
       <c r="E8">
-        <v>-1653.33</v>
+        <v>-1621.135</v>
       </c>
       <c r="F8">
-        <v>193.17</v>
+        <v>225.365</v>
       </c>
       <c r="G8">
         <v>152.5</v>
@@ -1949,28 +1949,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M8">
-        <v>9.716450999999999</v>
+        <v>11.3358595</v>
       </c>
       <c r="N8">
-        <v>336.6366102244898</v>
+        <v>335.0172017244898</v>
       </c>
       <c r="O8">
-        <v>84.15915255612245</v>
+        <v>83.75430043112246</v>
       </c>
       <c r="P8">
-        <v>252.4774576683674</v>
+        <v>251.2629012933674</v>
       </c>
       <c r="Q8">
-        <v>338.7774576683673</v>
+        <v>337.5629012933674</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07636327048317573</v>
+        <v>0.07661350194283822</v>
       </c>
       <c r="T8">
-        <v>0.4447328257426653</v>
+        <v>0.4483739983785149</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.64604619778248</v>
+        <v>30.55375388381357</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07389130680683954</v>
+        <v>0.0737376393594939</v>
       </c>
       <c r="C9">
-        <v>3025.16407420532</v>
+        <v>2997.702400855188</v>
       </c>
       <c r="D9">
-        <v>3098.029074205319</v>
+        <v>3102.762400855187</v>
       </c>
       <c r="E9">
-        <v>-1621.135</v>
+        <v>-1588.94</v>
       </c>
       <c r="F9">
-        <v>225.365</v>
+        <v>257.56</v>
       </c>
       <c r="G9">
         <v>152.5</v>
@@ -2031,28 +2031,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M9">
-        <v>11.3358595</v>
+        <v>12.955268</v>
       </c>
       <c r="N9">
-        <v>335.0172017244898</v>
+        <v>333.3977932244898</v>
       </c>
       <c r="O9">
-        <v>83.75430043112245</v>
+        <v>83.34944830612245</v>
       </c>
       <c r="P9">
-        <v>251.2629012933673</v>
+        <v>250.0483449183674</v>
       </c>
       <c r="Q9">
-        <v>337.5629012933674</v>
+        <v>336.3483449183674</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07661350194283822</v>
+        <v>0.0768691732168412</v>
       </c>
       <c r="T9">
-        <v>0.4483739983785149</v>
+        <v>0.4520943269412308</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.55375388381356</v>
+        <v>26.73453464833686</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0737376393594939</v>
+        <v>0.07358397191214824</v>
       </c>
       <c r="C10">
-        <v>2997.702400855188</v>
+        <v>2970.255213272342</v>
       </c>
       <c r="D10">
-        <v>3102.762400855187</v>
+        <v>3107.510213272342</v>
       </c>
       <c r="E10">
-        <v>-1588.94</v>
+        <v>-1556.745</v>
       </c>
       <c r="F10">
-        <v>257.56</v>
+        <v>289.755</v>
       </c>
       <c r="G10">
         <v>152.5</v>
@@ -2113,28 +2113,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M10">
-        <v>12.955268</v>
+        <v>14.5746765</v>
       </c>
       <c r="N10">
-        <v>333.3977932244898</v>
+        <v>331.7783847244898</v>
       </c>
       <c r="O10">
-        <v>83.34944830612245</v>
+        <v>82.94459618112245</v>
       </c>
       <c r="P10">
-        <v>250.0483449183674</v>
+        <v>248.8337885433673</v>
       </c>
       <c r="Q10">
-        <v>336.3483449183674</v>
+        <v>335.1337885433674</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0768691732168412</v>
+        <v>0.07713046363972334</v>
       </c>
       <c r="T10">
-        <v>0.4520943269412308</v>
+        <v>0.4558964209668634</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.73453464833686</v>
+        <v>23.76403079852166</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07358397191214824</v>
+        <v>0.0734303044648026</v>
       </c>
       <c r="C11">
-        <v>2970.255213272342</v>
+        <v>2942.822578056573</v>
       </c>
       <c r="D11">
-        <v>3107.510213272342</v>
+        <v>3112.272578056572</v>
       </c>
       <c r="E11">
-        <v>-1556.745</v>
+        <v>-1524.55</v>
       </c>
       <c r="F11">
-        <v>289.755</v>
+        <v>321.95</v>
       </c>
       <c r="G11">
         <v>152.5</v>
@@ -2195,28 +2195,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M11">
-        <v>14.5746765</v>
+        <v>16.194085</v>
       </c>
       <c r="N11">
-        <v>331.7783847244898</v>
+        <v>330.1589762244898</v>
       </c>
       <c r="O11">
-        <v>82.94459618112245</v>
+        <v>82.53974405612246</v>
       </c>
       <c r="P11">
-        <v>248.8337885433673</v>
+        <v>247.6192321683674</v>
       </c>
       <c r="Q11">
-        <v>335.1337885433674</v>
+        <v>333.9192321683674</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07713046363972334</v>
+        <v>0.07739756051644733</v>
       </c>
       <c r="T11">
-        <v>0.4558964209668634</v>
+        <v>0.4597830059708435</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.76403079852166</v>
+        <v>21.3876277186695</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0734303044648026</v>
+        <v>0.07327663701745694</v>
       </c>
       <c r="C12">
-        <v>2942.822578056573</v>
+        <v>2915.404562216561</v>
       </c>
       <c r="D12">
-        <v>3112.272578056572</v>
+        <v>3117.049562216561</v>
       </c>
       <c r="E12">
-        <v>-1524.55</v>
+        <v>-1492.355</v>
       </c>
       <c r="F12">
-        <v>321.95</v>
+        <v>354.145</v>
       </c>
       <c r="G12">
         <v>152.5</v>
@@ -2277,28 +2277,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M12">
-        <v>16.194085</v>
+        <v>17.8134935</v>
       </c>
       <c r="N12">
-        <v>330.1589762244898</v>
+        <v>328.5395677244898</v>
       </c>
       <c r="O12">
-        <v>82.53974405612246</v>
+        <v>82.13489193112245</v>
       </c>
       <c r="P12">
-        <v>247.6192321683674</v>
+        <v>246.4046757933673</v>
       </c>
       <c r="Q12">
-        <v>333.9192321683674</v>
+        <v>332.7046757933674</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07739756051644733</v>
+        <v>0.07767065957017635</v>
       </c>
       <c r="T12">
-        <v>0.4597830059708435</v>
+        <v>0.4637569299636771</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.38762771866949</v>
+        <v>19.44329792606317</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07327663701745694</v>
+        <v>0.0731229695701113</v>
       </c>
       <c r="C13">
-        <v>2915.404562216561</v>
+        <v>2888.001233173021</v>
       </c>
       <c r="D13">
-        <v>3117.049562216561</v>
+        <v>3121.841233173021</v>
       </c>
       <c r="E13">
-        <v>-1492.355</v>
+        <v>-1460.16</v>
       </c>
       <c r="F13">
-        <v>354.145</v>
+        <v>386.34</v>
       </c>
       <c r="G13">
         <v>152.5</v>
@@ -2359,28 +2359,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M13">
-        <v>17.8134935</v>
+        <v>19.432902</v>
       </c>
       <c r="N13">
-        <v>328.5395677244898</v>
+        <v>326.9201592244898</v>
       </c>
       <c r="O13">
-        <v>82.13489193112245</v>
+        <v>81.73003980612245</v>
       </c>
       <c r="P13">
-        <v>246.4046757933673</v>
+        <v>245.1901194183673</v>
       </c>
       <c r="Q13">
-        <v>332.7046757933674</v>
+        <v>331.4901194183673</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07767065957017635</v>
+        <v>0.07794996542058102</v>
       </c>
       <c r="T13">
-        <v>0.4637569299636771</v>
+        <v>0.4678211704108932</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.44329792606317</v>
+        <v>17.82302309889124</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0731229695701113</v>
+        <v>0.07296930212276566</v>
       </c>
       <c r="C14">
-        <v>2888.001233173021</v>
+        <v>2860.61265876188</v>
       </c>
       <c r="D14">
-        <v>3121.841233173021</v>
+        <v>3126.647658761879</v>
       </c>
       <c r="E14">
-        <v>-1460.16</v>
+        <v>-1427.965</v>
       </c>
       <c r="F14">
-        <v>386.34</v>
+        <v>418.535</v>
       </c>
       <c r="G14">
         <v>152.5</v>
@@ -2441,28 +2441,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M14">
-        <v>19.432902</v>
+        <v>21.0523105</v>
       </c>
       <c r="N14">
-        <v>326.9201592244898</v>
+        <v>325.3007507244898</v>
       </c>
       <c r="O14">
-        <v>81.73003980612245</v>
+        <v>81.32518768112246</v>
       </c>
       <c r="P14">
-        <v>245.1901194183673</v>
+        <v>243.9755630433674</v>
       </c>
       <c r="Q14">
-        <v>331.4901194183673</v>
+        <v>330.2755630433674</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07794996542058102</v>
+        <v>0.07823569209513294</v>
       </c>
       <c r="T14">
-        <v>0.4678211704108932</v>
+        <v>0.4719788416729879</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.82302309889124</v>
+        <v>16.45202132205345</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07296930212276566</v>
+        <v>0.07281563467542</v>
       </c>
       <c r="C15">
-        <v>2860.61265876188</v>
+        <v>2833.238907237467</v>
       </c>
       <c r="D15">
-        <v>3126.647658761879</v>
+        <v>3131.468907237467</v>
       </c>
       <c r="E15">
-        <v>-1427.965</v>
+        <v>-1395.77</v>
       </c>
       <c r="F15">
-        <v>418.535</v>
+        <v>450.73</v>
       </c>
       <c r="G15">
         <v>152.5</v>
@@ -2523,28 +2523,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M15">
-        <v>21.0523105</v>
+        <v>22.671719</v>
       </c>
       <c r="N15">
-        <v>325.3007507244898</v>
+        <v>323.6813422244898</v>
       </c>
       <c r="O15">
-        <v>81.32518768112246</v>
+        <v>80.92033555612245</v>
       </c>
       <c r="P15">
-        <v>243.9755630433674</v>
+        <v>242.7610066683674</v>
       </c>
       <c r="Q15">
-        <v>330.2755630433674</v>
+        <v>329.0610066683674</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07823569209513294</v>
+        <v>0.07852806357606978</v>
       </c>
       <c r="T15">
-        <v>0.4719788416729879</v>
+        <v>0.4762332029644336</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.45202132205345</v>
+        <v>15.27687694190678</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07281563467542</v>
+        <v>0.07266196722807436</v>
       </c>
       <c r="C16">
-        <v>2833.238907237467</v>
+        <v>2805.880047275753</v>
       </c>
       <c r="D16">
-        <v>3131.468907237467</v>
+        <v>3136.305047275753</v>
       </c>
       <c r="E16">
-        <v>-1395.77</v>
+        <v>-1363.575</v>
       </c>
       <c r="F16">
-        <v>450.73</v>
+        <v>482.9250000000001</v>
       </c>
       <c r="G16">
         <v>152.5</v>
@@ -2605,28 +2605,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M16">
-        <v>22.671719</v>
+        <v>24.2911275</v>
       </c>
       <c r="N16">
-        <v>323.6813422244898</v>
+        <v>322.0619337244898</v>
       </c>
       <c r="O16">
-        <v>80.92033555612245</v>
+        <v>80.51548343112245</v>
       </c>
       <c r="P16">
-        <v>242.7610066683674</v>
+        <v>241.5464502933673</v>
       </c>
       <c r="Q16">
-        <v>329.0610066683674</v>
+        <v>327.8464502933674</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07852806357606978</v>
+        <v>0.07882731438596983</v>
       </c>
       <c r="T16">
-        <v>0.4762332029644336</v>
+        <v>0.4805876668745016</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.27687694190678</v>
+        <v>14.25841847911299</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07266196722807436</v>
+        <v>0.07250829978072872</v>
       </c>
       <c r="C17">
-        <v>2805.880047275753</v>
+        <v>2778.536147977611</v>
       </c>
       <c r="D17">
-        <v>3136.305047275753</v>
+        <v>3141.156147977611</v>
       </c>
       <c r="E17">
-        <v>-1363.575</v>
+        <v>-1331.38</v>
       </c>
       <c r="F17">
-        <v>482.925</v>
+        <v>515.12</v>
       </c>
       <c r="G17">
         <v>152.5</v>
@@ -2687,28 +2687,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M17">
-        <v>24.2911275</v>
+        <v>25.910536</v>
       </c>
       <c r="N17">
-        <v>322.0619337244898</v>
+        <v>320.4425252244898</v>
       </c>
       <c r="O17">
-        <v>80.51548343112245</v>
+        <v>80.11063130612246</v>
       </c>
       <c r="P17">
-        <v>241.5464502933673</v>
+        <v>240.3318939183674</v>
       </c>
       <c r="Q17">
-        <v>327.8464502933674</v>
+        <v>326.6318939183674</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07882731438596983</v>
+        <v>0.07913369021515324</v>
       </c>
       <c r="T17">
-        <v>0.4805876668745016</v>
+        <v>0.485045808496714</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.25841847911299</v>
+        <v>13.36726732416843</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07250829978072872</v>
+        <v>0.07254588233338306</v>
       </c>
       <c r="C18">
-        <v>2778.536147977611</v>
+        <v>2745.153325176153</v>
       </c>
       <c r="D18">
-        <v>3141.156147977611</v>
+        <v>3139.968325176153</v>
       </c>
       <c r="E18">
-        <v>-1331.38</v>
+        <v>-1299.185</v>
       </c>
       <c r="F18">
-        <v>515.12</v>
+        <v>547.3150000000001</v>
       </c>
       <c r="G18">
         <v>152.5</v>
@@ -2769,45 +2769,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M18">
-        <v>25.910536</v>
+        <v>28.350917</v>
       </c>
       <c r="N18">
-        <v>320.4425252244898</v>
+        <v>318.0021442244898</v>
       </c>
       <c r="O18">
-        <v>80.11063130612246</v>
+        <v>79.50053605612246</v>
       </c>
       <c r="P18">
-        <v>240.3318939183674</v>
+        <v>238.5016081683674</v>
       </c>
       <c r="Q18">
-        <v>326.6318939183674</v>
+        <v>324.8016081683674</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07913369021515324</v>
+        <v>0.07944744859443743</v>
       </c>
       <c r="T18">
-        <v>0.485045808496714</v>
+        <v>0.489611375218257</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.36726732416843</v>
+        <v>12.21664404098428</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07254588233338306</v>
+        <v>0.07240346488603741</v>
       </c>
       <c r="C19">
-        <v>2745.153325176153</v>
+        <v>2717.46428278637</v>
       </c>
       <c r="D19">
-        <v>3139.968325176153</v>
+        <v>3144.474282786371</v>
       </c>
       <c r="E19">
-        <v>-1299.185</v>
+        <v>-1266.99</v>
       </c>
       <c r="F19">
-        <v>547.3150000000001</v>
+        <v>579.5100000000001</v>
       </c>
       <c r="G19">
         <v>152.5</v>
@@ -2851,28 +2851,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M19">
-        <v>28.350917</v>
+        <v>30.018618</v>
       </c>
       <c r="N19">
-        <v>318.0021442244898</v>
+        <v>316.3344432244898</v>
       </c>
       <c r="O19">
-        <v>79.50053605612246</v>
+        <v>79.08361080612245</v>
       </c>
       <c r="P19">
-        <v>238.5016081683674</v>
+        <v>237.2508324183673</v>
       </c>
       <c r="Q19">
-        <v>324.8016081683674</v>
+        <v>323.5508324183673</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07944744859443743</v>
+        <v>0.0797688596171188</v>
       </c>
       <c r="T19">
-        <v>0.489611375218257</v>
+        <v>0.494288297225691</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.21664404098428</v>
+        <v>11.53794159426293</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07240346488603742</v>
+        <v>0.07226104743869179</v>
       </c>
       <c r="C20">
-        <v>2717.46428278637</v>
+        <v>2689.788191375809</v>
       </c>
       <c r="D20">
-        <v>3144.47428278637</v>
+        <v>3148.993191375809</v>
       </c>
       <c r="E20">
-        <v>-1266.99</v>
+        <v>-1234.795</v>
       </c>
       <c r="F20">
-        <v>579.51</v>
+        <v>611.705</v>
       </c>
       <c r="G20">
         <v>152.5</v>
@@ -2933,28 +2933,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M20">
-        <v>30.018618</v>
+        <v>31.686319</v>
       </c>
       <c r="N20">
-        <v>316.3344432244898</v>
+        <v>314.6667422244898</v>
       </c>
       <c r="O20">
-        <v>79.08361080612245</v>
+        <v>78.66668555612245</v>
       </c>
       <c r="P20">
-        <v>237.2508324183673</v>
+        <v>236.0000566683673</v>
       </c>
       <c r="Q20">
-        <v>323.5508324183673</v>
+        <v>322.3000566683673</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0797688596171188</v>
+        <v>0.08009820671443429</v>
       </c>
       <c r="T20">
-        <v>0.494288297225691</v>
+        <v>0.4990806987888644</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.53794159426293</v>
+        <v>10.93068151035435</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07226104743869179</v>
+        <v>0.07211862999134612</v>
       </c>
       <c r="C21">
-        <v>2689.788191375809</v>
+        <v>2662.125106860191</v>
       </c>
       <c r="D21">
-        <v>3148.993191375809</v>
+        <v>3153.525106860191</v>
       </c>
       <c r="E21">
-        <v>-1234.795</v>
+        <v>-1202.6</v>
       </c>
       <c r="F21">
-        <v>611.705</v>
+        <v>643.9000000000001</v>
       </c>
       <c r="G21">
         <v>152.5</v>
@@ -3015,28 +3015,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M21">
-        <v>31.686319</v>
+        <v>33.35402000000001</v>
       </c>
       <c r="N21">
-        <v>314.6667422244898</v>
+        <v>312.9990412244898</v>
       </c>
       <c r="O21">
-        <v>78.66668555612245</v>
+        <v>78.24976030612245</v>
       </c>
       <c r="P21">
-        <v>236.0000566683673</v>
+        <v>234.7492809183674</v>
       </c>
       <c r="Q21">
-        <v>322.3000566683673</v>
+        <v>321.0492809183673</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08009820671443429</v>
+        <v>0.08043578748918265</v>
       </c>
       <c r="T21">
-        <v>0.4990806987888644</v>
+        <v>0.5039929103911169</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.93068151035435</v>
+        <v>10.38414743483663</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07211862999134612</v>
+        <v>0.07197621254400047</v>
       </c>
       <c r="C22">
-        <v>2662.125106860191</v>
+        <v>2634.475085477591</v>
       </c>
       <c r="D22">
-        <v>3153.525106860191</v>
+        <v>3158.070085477591</v>
       </c>
       <c r="E22">
-        <v>-1202.6</v>
+        <v>-1170.405</v>
       </c>
       <c r="F22">
-        <v>643.9000000000001</v>
+        <v>676.095</v>
       </c>
       <c r="G22">
         <v>152.5</v>
@@ -3097,28 +3097,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M22">
-        <v>33.35402000000001</v>
+        <v>35.021721</v>
       </c>
       <c r="N22">
-        <v>312.9990412244898</v>
+        <v>311.3313402244898</v>
       </c>
       <c r="O22">
-        <v>78.24976030612245</v>
+        <v>77.83283505612245</v>
       </c>
       <c r="P22">
-        <v>234.7492809183674</v>
+        <v>233.4985051683673</v>
       </c>
       <c r="Q22">
-        <v>321.0492809183673</v>
+        <v>319.7985051683673</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08043578748918265</v>
+        <v>0.08078191461265882</v>
       </c>
       <c r="T22">
-        <v>0.5039929103911169</v>
+        <v>0.5090294817807683</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.38414743483663</v>
+        <v>9.889664223653938</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07197621254400047</v>
+        <v>0.07211429509665482</v>
       </c>
       <c r="C23">
-        <v>2634.475085477591</v>
+        <v>2597.873253635687</v>
       </c>
       <c r="D23">
-        <v>3158.070085477591</v>
+        <v>3153.663253635687</v>
       </c>
       <c r="E23">
-        <v>-1170.405</v>
+        <v>-1138.21</v>
       </c>
       <c r="F23">
-        <v>676.095</v>
+        <v>708.29</v>
       </c>
       <c r="G23">
         <v>152.5</v>
@@ -3179,45 +3179,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M23">
-        <v>35.021721</v>
+        <v>37.893515</v>
       </c>
       <c r="N23">
-        <v>311.3313402244898</v>
+        <v>308.4595462244898</v>
       </c>
       <c r="O23">
-        <v>77.83283505612245</v>
+        <v>77.11488655612246</v>
       </c>
       <c r="P23">
-        <v>233.4985051683673</v>
+        <v>231.3446596683674</v>
       </c>
       <c r="Q23">
-        <v>319.7985051683673</v>
+        <v>317.6446596683674</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08078191461265882</v>
+        <v>0.0811369167905831</v>
       </c>
       <c r="T23">
-        <v>0.5090294817807683</v>
+        <v>0.5141951960265646</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.889664223653938</v>
+        <v>9.140167155896988</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07211429509665482</v>
+        <v>0.07198462764930919</v>
       </c>
       <c r="C24">
-        <v>2597.873253635687</v>
+        <v>2569.816169447997</v>
       </c>
       <c r="D24">
-        <v>3153.663253635687</v>
+        <v>3157.801169447997</v>
       </c>
       <c r="E24">
-        <v>-1138.21</v>
+        <v>-1106.015</v>
       </c>
       <c r="F24">
-        <v>708.29</v>
+        <v>740.485</v>
       </c>
       <c r="G24">
         <v>152.5</v>
@@ -3261,28 +3261,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M24">
-        <v>37.893515</v>
+        <v>39.6159475</v>
       </c>
       <c r="N24">
-        <v>308.4595462244898</v>
+        <v>306.7371137244898</v>
       </c>
       <c r="O24">
-        <v>77.11488655612246</v>
+        <v>76.68427843112245</v>
       </c>
       <c r="P24">
-        <v>231.3446596683674</v>
+        <v>230.0528352933674</v>
       </c>
       <c r="Q24">
-        <v>317.6446596683674</v>
+        <v>316.3528352933674</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0811369167905831</v>
+        <v>0.08150113980429763</v>
       </c>
       <c r="T24">
-        <v>0.5141951960265646</v>
+        <v>0.5194950846683557</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.140167155896988</v>
+        <v>8.742768583901466</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07198462764930919</v>
+        <v>0.07185496020196352</v>
       </c>
       <c r="C25">
-        <v>2569.816169447997</v>
+        <v>2541.769958230317</v>
       </c>
       <c r="D25">
-        <v>3157.801169447997</v>
+        <v>3161.949958230317</v>
       </c>
       <c r="E25">
-        <v>-1106.015</v>
+        <v>-1073.82</v>
       </c>
       <c r="F25">
-        <v>740.485</v>
+        <v>772.6800000000001</v>
       </c>
       <c r="G25">
         <v>152.5</v>
@@ -3343,28 +3343,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M25">
-        <v>39.6159475</v>
+        <v>41.33838</v>
       </c>
       <c r="N25">
-        <v>306.7371137244898</v>
+        <v>305.0146812244898</v>
       </c>
       <c r="O25">
-        <v>76.68427843112245</v>
+        <v>76.25367030612244</v>
       </c>
       <c r="P25">
-        <v>230.0528352933674</v>
+        <v>228.7610109183673</v>
       </c>
       <c r="Q25">
-        <v>316.3528352933674</v>
+        <v>315.0610109183673</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08150113980429763</v>
+        <v>0.08187494763416253</v>
       </c>
       <c r="T25">
-        <v>0.5194950846683557</v>
+        <v>0.524934444063878</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.742768583901466</v>
+        <v>8.378486559572238</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07185496020196352</v>
+        <v>0.07172529275461789</v>
       </c>
       <c r="C26">
-        <v>2541.769958230317</v>
+        <v>2513.734662894466</v>
       </c>
       <c r="D26">
-        <v>3161.949958230317</v>
+        <v>3166.109662894466</v>
       </c>
       <c r="E26">
-        <v>-1073.82</v>
+        <v>-1041.625</v>
       </c>
       <c r="F26">
-        <v>772.6799999999999</v>
+        <v>804.875</v>
       </c>
       <c r="G26">
         <v>152.5</v>
@@ -3425,28 +3425,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M26">
-        <v>41.33837999999999</v>
+        <v>43.0608125</v>
       </c>
       <c r="N26">
-        <v>305.0146812244898</v>
+        <v>303.2922487244898</v>
       </c>
       <c r="O26">
-        <v>76.25367030612246</v>
+        <v>75.82306218112245</v>
       </c>
       <c r="P26">
-        <v>228.7610109183674</v>
+        <v>227.4691865433674</v>
       </c>
       <c r="Q26">
-        <v>315.0610109183674</v>
+        <v>313.7691865433674</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08187494763416253</v>
+        <v>0.08225872367282384</v>
       </c>
       <c r="T26">
-        <v>0.524934444063878</v>
+        <v>0.5305188530432809</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.37848655957224</v>
+        <v>8.043347097189349</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07172529275461789</v>
+        <v>0.07159562530727223</v>
       </c>
       <c r="C27">
-        <v>2513.734662894466</v>
+        <v>2485.710326578376</v>
       </c>
       <c r="D27">
-        <v>3166.109662894466</v>
+        <v>3170.280326578376</v>
       </c>
       <c r="E27">
-        <v>-1041.625</v>
+        <v>-1009.43</v>
       </c>
       <c r="F27">
-        <v>804.875</v>
+        <v>837.0700000000001</v>
       </c>
       <c r="G27">
         <v>152.5</v>
@@ -3507,28 +3507,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M27">
-        <v>43.0608125</v>
+        <v>44.783245</v>
       </c>
       <c r="N27">
-        <v>303.2922487244898</v>
+        <v>301.5698162244898</v>
       </c>
       <c r="O27">
-        <v>75.82306218112245</v>
+        <v>75.39245405612245</v>
       </c>
       <c r="P27">
-        <v>227.4691865433674</v>
+        <v>226.1773621683673</v>
       </c>
       <c r="Q27">
-        <v>313.7691865433674</v>
+        <v>312.4773621683673</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08225872367282384</v>
+        <v>0.08265287203685437</v>
       </c>
       <c r="T27">
-        <v>0.5305188530432809</v>
+        <v>0.5362541919951003</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.043347097189349</v>
+        <v>7.733987593451296</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07159562530727223</v>
+        <v>0.07162795785992659</v>
       </c>
       <c r="C28">
-        <v>2485.710326578376</v>
+        <v>2452.47434441505</v>
       </c>
       <c r="D28">
-        <v>3170.280326578376</v>
+        <v>3169.23934441505</v>
       </c>
       <c r="E28">
-        <v>-1009.43</v>
+        <v>-977.2349999999999</v>
       </c>
       <c r="F28">
-        <v>837.0700000000001</v>
+        <v>869.2650000000001</v>
       </c>
       <c r="G28">
         <v>152.5</v>
@@ -3589,45 +3589,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M28">
-        <v>44.783245</v>
+        <v>47.20108950000001</v>
       </c>
       <c r="N28">
-        <v>301.5698162244898</v>
+        <v>299.1519717244898</v>
       </c>
       <c r="O28">
-        <v>75.39245405612245</v>
+        <v>74.78799293112245</v>
       </c>
       <c r="P28">
-        <v>226.1773621683673</v>
+        <v>224.3639787933673</v>
       </c>
       <c r="Q28">
-        <v>312.4773621683673</v>
+        <v>310.6639787933673</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08265287203685437</v>
+        <v>0.08305781898620081</v>
       </c>
       <c r="T28">
-        <v>0.5362541919951003</v>
+        <v>0.542146663520942</v>
       </c>
       <c r="U28">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.733987593451296</v>
+        <v>7.337819209119945</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07162795785992659</v>
+        <v>0.07150429041258094</v>
       </c>
       <c r="C29">
-        <v>2452.47434441505</v>
+        <v>2424.264651993507</v>
       </c>
       <c r="D29">
-        <v>3169.23934441505</v>
+        <v>3173.224651993507</v>
       </c>
       <c r="E29">
-        <v>-977.2349999999999</v>
+        <v>-945.04</v>
       </c>
       <c r="F29">
-        <v>869.2650000000001</v>
+        <v>901.46</v>
       </c>
       <c r="G29">
         <v>152.5</v>
@@ -3671,28 +3671,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M29">
-        <v>47.20108950000001</v>
+        <v>48.949278</v>
       </c>
       <c r="N29">
-        <v>299.1519717244898</v>
+        <v>297.4037832244898</v>
       </c>
       <c r="O29">
-        <v>74.78799293112245</v>
+        <v>74.35094580612245</v>
       </c>
       <c r="P29">
-        <v>224.3639787933673</v>
+        <v>223.0528374183673</v>
       </c>
       <c r="Q29">
-        <v>310.6639787933673</v>
+        <v>309.3528374183674</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08305781898620081</v>
+        <v>0.08347401446191798</v>
       </c>
       <c r="T29">
-        <v>0.542146663520942</v>
+        <v>0.5482028148113903</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.337819209119945</v>
+        <v>7.075754237365663</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07150429041258094</v>
+        <v>0.07138062296523529</v>
       </c>
       <c r="C30">
-        <v>2424.264651993507</v>
+        <v>2396.064995212903</v>
       </c>
       <c r="D30">
-        <v>3173.224651993507</v>
+        <v>3177.219995212903</v>
       </c>
       <c r="E30">
-        <v>-945.04</v>
+        <v>-912.8449999999999</v>
       </c>
       <c r="F30">
-        <v>901.46</v>
+        <v>933.6550000000001</v>
       </c>
       <c r="G30">
         <v>152.5</v>
@@ -3753,28 +3753,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M30">
-        <v>48.949278</v>
+        <v>50.6974665</v>
       </c>
       <c r="N30">
-        <v>297.4037832244898</v>
+        <v>295.6555947244898</v>
       </c>
       <c r="O30">
-        <v>74.35094580612245</v>
+        <v>73.91389868112245</v>
       </c>
       <c r="P30">
-        <v>223.0528374183673</v>
+        <v>221.7416960433673</v>
       </c>
       <c r="Q30">
-        <v>309.3528374183674</v>
+        <v>308.0416960433673</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08347401446191798</v>
+        <v>0.08390193375385252</v>
       </c>
       <c r="T30">
-        <v>0.5482028148113903</v>
+        <v>0.5544295619128373</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.075754237365663</v>
+        <v>6.83176271193926</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07138062296523529</v>
+        <v>0.07125695551788963</v>
       </c>
       <c r="C31">
-        <v>2396.064995212903</v>
+        <v>2367.875412028044</v>
       </c>
       <c r="D31">
-        <v>3177.219995212903</v>
+        <v>3181.225412028044</v>
       </c>
       <c r="E31">
-        <v>-912.845</v>
+        <v>-880.6500000000001</v>
       </c>
       <c r="F31">
-        <v>933.655</v>
+        <v>965.8499999999999</v>
       </c>
       <c r="G31">
         <v>152.5</v>
@@ -3835,28 +3835,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M31">
-        <v>50.6974665</v>
+        <v>52.445655</v>
       </c>
       <c r="N31">
-        <v>295.6555947244898</v>
+        <v>293.9074062244898</v>
       </c>
       <c r="O31">
-        <v>73.91389868112245</v>
+        <v>73.47685155612245</v>
       </c>
       <c r="P31">
-        <v>221.7416960433673</v>
+        <v>220.4305546683674</v>
       </c>
       <c r="Q31">
-        <v>308.0416960433673</v>
+        <v>306.7305546683673</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08390193375385252</v>
+        <v>0.08434207931127091</v>
       </c>
       <c r="T31">
-        <v>0.5544295619128373</v>
+        <v>0.5608342160743256</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.831762711939261</v>
+        <v>6.604037288207953</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07125695551788963</v>
+        <v>0.07113328807054399</v>
       </c>
       <c r="C32">
-        <v>2367.875412028044</v>
+        <v>2339.695940585372</v>
       </c>
       <c r="D32">
-        <v>3181.225412028044</v>
+        <v>3185.240940585372</v>
       </c>
       <c r="E32">
-        <v>-880.6500000000001</v>
+        <v>-848.455</v>
       </c>
       <c r="F32">
-        <v>965.8499999999999</v>
+        <v>998.045</v>
       </c>
       <c r="G32">
         <v>152.5</v>
@@ -3917,28 +3917,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M32">
-        <v>52.445655</v>
+        <v>54.1938435</v>
       </c>
       <c r="N32">
-        <v>293.9074062244898</v>
+        <v>292.1592177244898</v>
       </c>
       <c r="O32">
-        <v>73.47685155612245</v>
+        <v>73.03980443112245</v>
       </c>
       <c r="P32">
-        <v>220.4305546683674</v>
+        <v>219.1194132933674</v>
       </c>
       <c r="Q32">
-        <v>306.7305546683673</v>
+        <v>305.4194132933674</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08434207931127091</v>
+        <v>0.08479498271093333</v>
       </c>
       <c r="T32">
-        <v>0.5608342160743256</v>
+        <v>0.5674245123854222</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.604037288207953</v>
+        <v>6.391003827298017</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07113328807054399</v>
+        <v>0.07100962062319834</v>
       </c>
       <c r="C33">
-        <v>2339.695940585372</v>
+        <v>2311.52661922418</v>
       </c>
       <c r="D33">
-        <v>3185.240940585372</v>
+        <v>3189.26661922418</v>
       </c>
       <c r="E33">
-        <v>-848.455</v>
+        <v>-816.26</v>
       </c>
       <c r="F33">
-        <v>998.045</v>
+        <v>1030.24</v>
       </c>
       <c r="G33">
         <v>152.5</v>
@@ -3999,28 +3999,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M33">
-        <v>54.1938435</v>
+        <v>55.942032</v>
       </c>
       <c r="N33">
-        <v>292.1592177244898</v>
+        <v>290.4110292244898</v>
       </c>
       <c r="O33">
-        <v>73.03980443112245</v>
+        <v>72.60275730612246</v>
       </c>
       <c r="P33">
-        <v>219.1194132933674</v>
+        <v>217.8082719183674</v>
       </c>
       <c r="Q33">
-        <v>305.4194132933674</v>
+        <v>304.1082719183674</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08479498271093333</v>
+        <v>0.0852612067988211</v>
       </c>
       <c r="T33">
-        <v>0.5674245123854222</v>
+        <v>0.574208640940963</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.391003827298017</v>
+        <v>6.191284957694955</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07100962062319834</v>
+        <v>0.07113345317585269</v>
       </c>
       <c r="C34">
-        <v>2311.52661922418</v>
+        <v>2275.300572795901</v>
       </c>
       <c r="D34">
-        <v>3189.26661922418</v>
+        <v>3185.235572795901</v>
       </c>
       <c r="E34">
-        <v>-816.26</v>
+        <v>-784.0650000000001</v>
       </c>
       <c r="F34">
-        <v>1030.24</v>
+        <v>1062.435</v>
       </c>
       <c r="G34">
         <v>152.5</v>
@@ -4081,45 +4081,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M34">
-        <v>55.942032</v>
+        <v>58.7526555</v>
       </c>
       <c r="N34">
-        <v>290.4110292244898</v>
+        <v>287.6004057244898</v>
       </c>
       <c r="O34">
-        <v>72.60275730612246</v>
+        <v>71.90010143112245</v>
       </c>
       <c r="P34">
-        <v>217.8082719183674</v>
+        <v>215.7003042933674</v>
       </c>
       <c r="Q34">
-        <v>304.1082719183674</v>
+        <v>302.0003042933674</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0852612067988211</v>
+        <v>0.08574134802366075</v>
       </c>
       <c r="T34">
-        <v>0.574208640940963</v>
+        <v>0.581195280796669</v>
       </c>
       <c r="U34">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.191284957694955</v>
+        <v>5.895104796148147</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07113345317585269</v>
+        <v>0.07101728572850705</v>
       </c>
       <c r="C35">
-        <v>2275.300572795901</v>
+        <v>2246.886805466953</v>
       </c>
       <c r="D35">
-        <v>3185.235572795901</v>
+        <v>3189.016805466953</v>
       </c>
       <c r="E35">
-        <v>-784.0650000000001</v>
+        <v>-751.8699999999999</v>
       </c>
       <c r="F35">
-        <v>1062.435</v>
+        <v>1094.63</v>
       </c>
       <c r="G35">
         <v>152.5</v>
@@ -4163,28 +4163,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M35">
-        <v>58.7526555</v>
+        <v>60.53303900000001</v>
       </c>
       <c r="N35">
-        <v>287.6004057244898</v>
+        <v>285.8200222244898</v>
       </c>
       <c r="O35">
-        <v>71.90010143112245</v>
+        <v>71.45500555612244</v>
       </c>
       <c r="P35">
-        <v>215.7003042933674</v>
+        <v>214.3650166683673</v>
       </c>
       <c r="Q35">
-        <v>302.0003042933674</v>
+        <v>300.6650166683673</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08574134802366075</v>
+        <v>0.08623603898258644</v>
       </c>
       <c r="T35">
-        <v>0.581195280796669</v>
+        <v>0.5883936370116389</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.895104796148147</v>
+        <v>5.721719360967318</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07101728572850705</v>
+        <v>0.07090111828116141</v>
       </c>
       <c r="C36">
-        <v>2246.886805466953</v>
+        <v>2218.482026304411</v>
       </c>
       <c r="D36">
-        <v>3189.016805466953</v>
+        <v>3192.807026304411</v>
       </c>
       <c r="E36">
-        <v>-751.8699999999999</v>
+        <v>-719.675</v>
       </c>
       <c r="F36">
-        <v>1094.63</v>
+        <v>1126.825</v>
       </c>
       <c r="G36">
         <v>152.5</v>
@@ -4245,28 +4245,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M36">
-        <v>60.53303900000001</v>
+        <v>62.3134225</v>
       </c>
       <c r="N36">
-        <v>285.8200222244898</v>
+        <v>284.0396387244898</v>
       </c>
       <c r="O36">
-        <v>71.45500555612244</v>
+        <v>71.00990968112245</v>
       </c>
       <c r="P36">
-        <v>214.3650166683673</v>
+        <v>213.0297290433674</v>
       </c>
       <c r="Q36">
-        <v>300.6650166683673</v>
+        <v>299.3297290433674</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08623603898258644</v>
+        <v>0.08674595120178678</v>
       </c>
       <c r="T36">
-        <v>0.5883936370116389</v>
+        <v>0.5958134811101464</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.721719360967318</v>
+        <v>5.558241664939682</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07090111828116141</v>
+        <v>0.07078495083381575</v>
       </c>
       <c r="C37">
-        <v>2218.482026304411</v>
+        <v>2190.086267394348</v>
       </c>
       <c r="D37">
-        <v>3192.807026304411</v>
+        <v>3196.606267394349</v>
       </c>
       <c r="E37">
-        <v>-719.675</v>
+        <v>-687.4799999999998</v>
       </c>
       <c r="F37">
-        <v>1126.825</v>
+        <v>1159.02</v>
       </c>
       <c r="G37">
         <v>152.5</v>
@@ -4327,28 +4327,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M37">
-        <v>62.3134225</v>
+        <v>64.09380600000001</v>
       </c>
       <c r="N37">
-        <v>284.0396387244898</v>
+        <v>282.2592552244898</v>
       </c>
       <c r="O37">
-        <v>71.00990968112245</v>
+        <v>70.56481380612244</v>
       </c>
       <c r="P37">
-        <v>213.0297290433674</v>
+        <v>211.6944414183673</v>
       </c>
       <c r="Q37">
-        <v>299.3297290433674</v>
+        <v>297.9944414183673</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08674595120178678</v>
+        <v>0.08727179817783712</v>
       </c>
       <c r="T37">
-        <v>0.5958134811101464</v>
+        <v>0.6034651953367322</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.558241664939682</v>
+        <v>5.4038460631358</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07078495083381575</v>
+        <v>0.07066878338647012</v>
       </c>
       <c r="C38">
-        <v>2190.086267394349</v>
+        <v>2161.699560975739</v>
       </c>
       <c r="D38">
-        <v>3196.606267394349</v>
+        <v>3200.414560975739</v>
       </c>
       <c r="E38">
-        <v>-687.48</v>
+        <v>-655.2850000000001</v>
       </c>
       <c r="F38">
-        <v>1159.02</v>
+        <v>1191.215</v>
       </c>
       <c r="G38">
         <v>152.5</v>
@@ -4409,28 +4409,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M38">
-        <v>64.093806</v>
+        <v>65.8741895</v>
       </c>
       <c r="N38">
-        <v>282.2592552244898</v>
+        <v>280.4788717244898</v>
       </c>
       <c r="O38">
-        <v>70.56481380612246</v>
+        <v>70.11971793112245</v>
       </c>
       <c r="P38">
-        <v>211.6944414183674</v>
+        <v>210.3591537933673</v>
       </c>
       <c r="Q38">
-        <v>297.9944414183674</v>
+        <v>296.6591537933674</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08727179817783712</v>
+        <v>0.08781433870868272</v>
       </c>
       <c r="T38">
-        <v>0.6034651953367322</v>
+        <v>0.6113598211260667</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.403846063135802</v>
+        <v>5.257796169537537</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07066878338647012</v>
+        <v>0.07055261593912446</v>
       </c>
       <c r="C39">
-        <v>2161.699560975739</v>
+        <v>2133.321939441373</v>
       </c>
       <c r="D39">
-        <v>3200.414560975739</v>
+        <v>3204.231939441373</v>
       </c>
       <c r="E39">
-        <v>-655.2850000000001</v>
+        <v>-623.0899999999999</v>
       </c>
       <c r="F39">
-        <v>1191.215</v>
+        <v>1223.41</v>
       </c>
       <c r="G39">
         <v>152.5</v>
@@ -4491,28 +4491,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M39">
-        <v>65.8741895</v>
+        <v>67.65457300000001</v>
       </c>
       <c r="N39">
-        <v>280.4788717244898</v>
+        <v>278.6984882244898</v>
       </c>
       <c r="O39">
-        <v>70.11971793112245</v>
+        <v>69.67462205612244</v>
       </c>
       <c r="P39">
-        <v>210.3591537933673</v>
+        <v>209.0238661683673</v>
       </c>
       <c r="Q39">
-        <v>296.6591537933674</v>
+        <v>295.3238661683673</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08781433870868272</v>
+        <v>0.08837438054697494</v>
       </c>
       <c r="T39">
-        <v>0.6113598211260667</v>
+        <v>0.6195091122634443</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.257796169537537</v>
+        <v>5.119433112444442</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07055261593912446</v>
+        <v>0.07043644849177881</v>
       </c>
       <c r="C40">
-        <v>2133.321939441373</v>
+        <v>2104.953435338774</v>
       </c>
       <c r="D40">
-        <v>3204.231939441373</v>
+        <v>3208.058435338774</v>
       </c>
       <c r="E40">
-        <v>-623.0899999999999</v>
+        <v>-590.895</v>
       </c>
       <c r="F40">
-        <v>1223.41</v>
+        <v>1255.605</v>
       </c>
       <c r="G40">
         <v>152.5</v>
@@ -4573,28 +4573,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M40">
-        <v>67.65457300000001</v>
+        <v>69.4349565</v>
       </c>
       <c r="N40">
-        <v>278.6984882244898</v>
+        <v>276.9181047244898</v>
       </c>
       <c r="O40">
-        <v>69.67462205612244</v>
+        <v>69.22952618112245</v>
       </c>
       <c r="P40">
-        <v>209.0238661683673</v>
+        <v>207.6885785433674</v>
       </c>
       <c r="Q40">
-        <v>295.3238661683673</v>
+        <v>293.9885785433673</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08837438054697494</v>
+        <v>0.08895278441275216</v>
       </c>
       <c r="T40">
-        <v>0.6195091122634443</v>
+        <v>0.6279255932741785</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.119433112444442</v>
+        <v>4.98816559674074</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07043644849177881</v>
+        <v>0.07032028104443316</v>
       </c>
       <c r="C41">
-        <v>2104.953435338774</v>
+        <v>2076.594081371125</v>
       </c>
       <c r="D41">
-        <v>3208.058435338774</v>
+        <v>3211.894081371126</v>
       </c>
       <c r="E41">
-        <v>-590.895</v>
+        <v>-558.6999999999998</v>
       </c>
       <c r="F41">
-        <v>1255.605</v>
+        <v>1287.8</v>
       </c>
       <c r="G41">
         <v>152.5</v>
@@ -4655,28 +4655,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M41">
-        <v>69.4349565</v>
+        <v>71.21534000000001</v>
       </c>
       <c r="N41">
-        <v>276.9181047244898</v>
+        <v>275.1377212244898</v>
       </c>
       <c r="O41">
-        <v>69.22952618112245</v>
+        <v>68.78443030612245</v>
       </c>
       <c r="P41">
-        <v>207.6885785433674</v>
+        <v>206.3532909183673</v>
       </c>
       <c r="Q41">
-        <v>293.9885785433673</v>
+        <v>292.6532909183674</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08895278441275216</v>
+        <v>0.08955046840738862</v>
       </c>
       <c r="T41">
-        <v>0.6279255932741785</v>
+        <v>0.6366226236519372</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.98816559674074</v>
+        <v>4.86346145682222</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07032028104443316</v>
+        <v>0.07020411359708752</v>
       </c>
       <c r="C42">
-        <v>2076.594081371125</v>
+        <v>2048.243910398201</v>
       </c>
       <c r="D42">
-        <v>3211.894081371126</v>
+        <v>3215.738910398202</v>
       </c>
       <c r="E42">
-        <v>-558.6999999999998</v>
+        <v>-526.5049999999999</v>
       </c>
       <c r="F42">
-        <v>1287.8</v>
+        <v>1319.995</v>
       </c>
       <c r="G42">
         <v>152.5</v>
@@ -4737,28 +4737,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M42">
-        <v>71.21534000000001</v>
+        <v>72.99572350000001</v>
       </c>
       <c r="N42">
-        <v>275.1377212244898</v>
+        <v>273.3573377244898</v>
       </c>
       <c r="O42">
-        <v>68.78443030612245</v>
+        <v>68.33933443112245</v>
       </c>
       <c r="P42">
-        <v>206.3532909183673</v>
+        <v>205.0180032933674</v>
       </c>
       <c r="Q42">
-        <v>292.6532909183674</v>
+        <v>291.3180032933674</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08955046840738862</v>
+        <v>0.09016841287641952</v>
       </c>
       <c r="T42">
-        <v>0.6366226236519372</v>
+        <v>0.6456144686187725</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.86346145682222</v>
+        <v>4.744840445680215</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07020411359708752</v>
+        <v>0.07008794614974187</v>
       </c>
       <c r="C43">
-        <v>2048.243910398201</v>
+        <v>2019.902955437306</v>
       </c>
       <c r="D43">
-        <v>3215.738910398202</v>
+        <v>3219.592955437306</v>
       </c>
       <c r="E43">
-        <v>-526.5049999999999</v>
+        <v>-494.3099999999999</v>
       </c>
       <c r="F43">
-        <v>1319.995</v>
+        <v>1352.19</v>
       </c>
       <c r="G43">
         <v>152.5</v>
@@ -4819,28 +4819,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M43">
-        <v>72.99572350000001</v>
+        <v>74.77610700000001</v>
       </c>
       <c r="N43">
-        <v>273.3573377244898</v>
+        <v>271.5769542244898</v>
       </c>
       <c r="O43">
-        <v>68.33933443112245</v>
+        <v>67.89423855612245</v>
       </c>
       <c r="P43">
-        <v>205.0180032933674</v>
+        <v>203.6827156683673</v>
       </c>
       <c r="Q43">
-        <v>291.3180032933674</v>
+        <v>289.9827156683673</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09016841287641952</v>
+        <v>0.09080766577541702</v>
       </c>
       <c r="T43">
-        <v>0.6456144686187725</v>
+        <v>0.6549163772051537</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.744840445680215</v>
+        <v>4.631868054116401</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07008794614974187</v>
+        <v>0.06997177870239622</v>
       </c>
       <c r="C44">
-        <v>2019.902955437306</v>
+        <v>1991.571249664215</v>
       </c>
       <c r="D44">
-        <v>3219.592955437306</v>
+        <v>3223.456249664215</v>
       </c>
       <c r="E44">
-        <v>-494.3099999999999</v>
+        <v>-462.115</v>
       </c>
       <c r="F44">
-        <v>1352.19</v>
+        <v>1384.385</v>
       </c>
       <c r="G44">
         <v>152.5</v>
@@ -4901,28 +4901,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M44">
-        <v>74.77610700000001</v>
+        <v>76.5564905</v>
       </c>
       <c r="N44">
-        <v>271.5769542244898</v>
+        <v>269.7965707244898</v>
       </c>
       <c r="O44">
-        <v>67.89423855612245</v>
+        <v>67.44914268112245</v>
       </c>
       <c r="P44">
-        <v>203.6827156683673</v>
+        <v>202.3474280433674</v>
       </c>
       <c r="Q44">
-        <v>289.9827156683673</v>
+        <v>288.6474280433674</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09080766577541702</v>
+        <v>0.09146934860069512</v>
       </c>
       <c r="T44">
-        <v>0.6549163772051537</v>
+        <v>0.6645446685489519</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.631868054116401</v>
+        <v>4.524150192392764</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06997177870239622</v>
+        <v>0.0706806112550506</v>
       </c>
       <c r="C45">
-        <v>1991.571249664215</v>
+        <v>1935.946395523949</v>
       </c>
       <c r="D45">
-        <v>3223.456249664215</v>
+        <v>3200.026395523949</v>
       </c>
       <c r="E45">
-        <v>-462.115</v>
+        <v>-429.9200000000001</v>
       </c>
       <c r="F45">
-        <v>1384.385</v>
+        <v>1416.58</v>
       </c>
       <c r="G45">
         <v>152.5</v>
@@ -4983,45 +4983,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M45">
-        <v>76.5564905</v>
+        <v>81.87832400000001</v>
       </c>
       <c r="N45">
-        <v>269.7965707244898</v>
+        <v>264.4747372244898</v>
       </c>
       <c r="O45">
-        <v>67.44914268112245</v>
+        <v>66.11868430612245</v>
       </c>
       <c r="P45">
-        <v>202.3474280433674</v>
+        <v>198.3560529183673</v>
       </c>
       <c r="Q45">
-        <v>288.6474280433674</v>
+        <v>284.6560529183673</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09146934860069512</v>
+        <v>0.09215466295544747</v>
       </c>
       <c r="T45">
-        <v>0.6645446685489519</v>
+        <v>0.674516827440743</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.524150192392764</v>
+        <v>4.230094661249902</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0706806112550506</v>
+        <v>0.07058319380770493</v>
       </c>
       <c r="C46">
-        <v>1935.946395523949</v>
+        <v>1906.951237338631</v>
       </c>
       <c r="D46">
-        <v>3200.026395523949</v>
+        <v>3203.226237338631</v>
       </c>
       <c r="E46">
-        <v>-429.9200000000001</v>
+        <v>-397.7249999999999</v>
       </c>
       <c r="F46">
-        <v>1416.58</v>
+        <v>1448.775</v>
       </c>
       <c r="G46">
         <v>152.5</v>
@@ -5065,28 +5065,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M46">
-        <v>81.87832400000001</v>
+        <v>83.73919500000001</v>
       </c>
       <c r="N46">
-        <v>264.4747372244898</v>
+        <v>262.6138662244898</v>
       </c>
       <c r="O46">
-        <v>66.11868430612245</v>
+        <v>65.65346655612245</v>
       </c>
       <c r="P46">
-        <v>198.3560529183673</v>
+        <v>196.9603996683674</v>
       </c>
       <c r="Q46">
-        <v>284.6560529183673</v>
+        <v>283.2603996683674</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09215466295544747</v>
+        <v>0.09286489783219078</v>
       </c>
       <c r="T46">
-        <v>0.674516827440743</v>
+        <v>0.6848516102922354</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.230094661249902</v>
+        <v>4.136092557666572</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07058319380770493</v>
+        <v>0.0704857763603593</v>
       </c>
       <c r="C47">
-        <v>1906.951237338631</v>
+        <v>1877.962484873152</v>
       </c>
       <c r="D47">
-        <v>3203.226237338631</v>
+        <v>3206.432484873152</v>
       </c>
       <c r="E47">
-        <v>-397.7249999999999</v>
+        <v>-365.53</v>
       </c>
       <c r="F47">
-        <v>1448.775</v>
+        <v>1480.97</v>
       </c>
       <c r="G47">
         <v>152.5</v>
@@ -5147,28 +5147,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M47">
-        <v>83.73919500000001</v>
+        <v>85.60006600000001</v>
       </c>
       <c r="N47">
-        <v>262.6138662244898</v>
+        <v>260.7529952244898</v>
       </c>
       <c r="O47">
-        <v>65.65346655612245</v>
+        <v>65.18824880612244</v>
       </c>
       <c r="P47">
-        <v>196.9603996683674</v>
+        <v>195.5647464183673</v>
       </c>
       <c r="Q47">
-        <v>283.2603996683674</v>
+        <v>281.8647464183674</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09286489783219078</v>
+        <v>0.09360143770436904</v>
       </c>
       <c r="T47">
-        <v>0.6848516102922354</v>
+        <v>0.6955691628789684</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.136092557666572</v>
+        <v>4.046177502065124</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0704857763603593</v>
+        <v>0.07162210891301363</v>
       </c>
       <c r="C48">
-        <v>1877.962484873152</v>
+        <v>1808.762607055304</v>
       </c>
       <c r="D48">
-        <v>3206.432484873152</v>
+        <v>3169.427607055304</v>
       </c>
       <c r="E48">
-        <v>-365.53</v>
+        <v>-333.3349999999998</v>
       </c>
       <c r="F48">
-        <v>1480.97</v>
+        <v>1513.165</v>
       </c>
       <c r="G48">
         <v>152.5</v>
@@ -5229,45 +5229,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M48">
-        <v>85.60006600000001</v>
+        <v>92.75701450000001</v>
       </c>
       <c r="N48">
-        <v>260.7529952244898</v>
+        <v>253.5960467244898</v>
       </c>
       <c r="O48">
-        <v>65.18824880612244</v>
+        <v>63.39901168112245</v>
       </c>
       <c r="P48">
-        <v>195.5647464183673</v>
+        <v>190.1970350433674</v>
       </c>
       <c r="Q48">
-        <v>281.8647464183674</v>
+        <v>276.4970350433674</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09360143770436904</v>
+        <v>0.09436577153398798</v>
       </c>
       <c r="T48">
-        <v>0.6955691628789684</v>
+        <v>0.7066911514123705</v>
       </c>
       <c r="U48">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.046177502065124</v>
+        <v>3.73398241730268</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07162210891301363</v>
+        <v>0.071550941465668</v>
       </c>
       <c r="C49">
-        <v>1808.762607055304</v>
+        <v>1778.860098214793</v>
       </c>
       <c r="D49">
-        <v>3169.427607055304</v>
+        <v>3171.720098214793</v>
       </c>
       <c r="E49">
-        <v>-333.3349999999998</v>
+        <v>-301.1399999999999</v>
       </c>
       <c r="F49">
-        <v>1513.165</v>
+        <v>1545.36</v>
       </c>
       <c r="G49">
         <v>152.5</v>
@@ -5311,28 +5311,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M49">
-        <v>92.75701450000001</v>
+        <v>94.73056800000001</v>
       </c>
       <c r="N49">
-        <v>253.5960467244898</v>
+        <v>251.6224932244898</v>
       </c>
       <c r="O49">
-        <v>63.39901168112245</v>
+        <v>62.90562330612245</v>
       </c>
       <c r="P49">
-        <v>190.1970350433674</v>
+        <v>188.7168699183674</v>
       </c>
       <c r="Q49">
-        <v>276.4970350433674</v>
+        <v>275.0168699183674</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09436577153398798</v>
+        <v>0.09515950281859228</v>
       </c>
       <c r="T49">
-        <v>0.7066911514123705</v>
+        <v>0.7182409087355188</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.73398241730268</v>
+        <v>3.656191116942208</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.071550941465668</v>
+        <v>0.07147977401832234</v>
       </c>
       <c r="C50">
-        <v>1778.860098214793</v>
+        <v>1748.960908156416</v>
       </c>
       <c r="D50">
-        <v>3171.720098214793</v>
+        <v>3174.015908156416</v>
       </c>
       <c r="E50">
-        <v>-301.1400000000001</v>
+        <v>-268.9449999999999</v>
       </c>
       <c r="F50">
-        <v>1545.36</v>
+        <v>1577.555</v>
       </c>
       <c r="G50">
         <v>152.5</v>
@@ -5393,28 +5393,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M50">
-        <v>94.73056799999999</v>
+        <v>96.7041215</v>
       </c>
       <c r="N50">
-        <v>251.6224932244898</v>
+        <v>249.6489397244898</v>
       </c>
       <c r="O50">
-        <v>62.90562330612245</v>
+        <v>62.41223493112246</v>
       </c>
       <c r="P50">
-        <v>188.7168699183674</v>
+        <v>187.2367047933674</v>
       </c>
       <c r="Q50">
-        <v>275.0168699183674</v>
+        <v>273.5367047933674</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09515950281859228</v>
+        <v>0.09598436082023987</v>
       </c>
       <c r="T50">
-        <v>0.7182409087355188</v>
+        <v>0.7302435977183984</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.656191116942209</v>
+        <v>3.58157497169849</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07147977401832234</v>
+        <v>0.0714086065709767</v>
       </c>
       <c r="C51">
-        <v>1748.960908156416</v>
+        <v>1719.065044092166</v>
       </c>
       <c r="D51">
-        <v>3174.015908156416</v>
+        <v>3176.315044092166</v>
       </c>
       <c r="E51">
-        <v>-268.9449999999999</v>
+        <v>-236.75</v>
       </c>
       <c r="F51">
-        <v>1577.555</v>
+        <v>1609.75</v>
       </c>
       <c r="G51">
         <v>152.5</v>
@@ -5475,28 +5475,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M51">
-        <v>96.7041215</v>
+        <v>98.67767499999999</v>
       </c>
       <c r="N51">
-        <v>249.6489397244898</v>
+        <v>247.6753862244898</v>
       </c>
       <c r="O51">
-        <v>62.41223493112246</v>
+        <v>61.91884655612245</v>
       </c>
       <c r="P51">
-        <v>187.2367047933674</v>
+        <v>185.7565396683674</v>
       </c>
       <c r="Q51">
-        <v>273.5367047933674</v>
+        <v>272.0565396683673</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09598436082023987</v>
+        <v>0.09684221314195338</v>
       </c>
       <c r="T51">
-        <v>0.7302435977183984</v>
+        <v>0.7427263942605934</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.58157497169849</v>
+        <v>3.50994347226452</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0714086065709767</v>
+        <v>0.07240843912363104</v>
       </c>
       <c r="C52">
-        <v>1719.065044092166</v>
+        <v>1654.871684517395</v>
       </c>
       <c r="D52">
-        <v>3176.315044092166</v>
+        <v>3144.316684517395</v>
       </c>
       <c r="E52">
-        <v>-236.75</v>
+        <v>-204.5550000000001</v>
       </c>
       <c r="F52">
-        <v>1609.75</v>
+        <v>1641.945</v>
       </c>
       <c r="G52">
         <v>152.5</v>
@@ -5557,45 +5557,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M52">
-        <v>98.67767499999999</v>
+        <v>105.2486745</v>
       </c>
       <c r="N52">
-        <v>247.6753862244898</v>
+        <v>241.1043867244898</v>
       </c>
       <c r="O52">
-        <v>61.91884655612245</v>
+        <v>60.27609668112245</v>
       </c>
       <c r="P52">
-        <v>185.7565396683674</v>
+        <v>180.8282900433674</v>
       </c>
       <c r="Q52">
-        <v>272.0565396683673</v>
+        <v>267.1282900433674</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09684221314195338</v>
+        <v>0.09773507984414499</v>
       </c>
       <c r="T52">
-        <v>0.7427263942605934</v>
+        <v>0.7557186927024697</v>
       </c>
       <c r="U52">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.50994347226452</v>
+        <v>3.290806871154371</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07240843912363104</v>
+        <v>0.07235827167628539</v>
       </c>
       <c r="C53">
-        <v>1654.871684517395</v>
+        <v>1624.266858831854</v>
       </c>
       <c r="D53">
-        <v>3144.316684517395</v>
+        <v>3145.906858831854</v>
       </c>
       <c r="E53">
-        <v>-204.5550000000001</v>
+        <v>-172.3599999999999</v>
       </c>
       <c r="F53">
-        <v>1641.945</v>
+        <v>1674.14</v>
       </c>
       <c r="G53">
         <v>152.5</v>
@@ -5639,28 +5639,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M53">
-        <v>105.2486745</v>
+        <v>107.312374</v>
       </c>
       <c r="N53">
-        <v>241.1043867244898</v>
+        <v>239.0406872244898</v>
       </c>
       <c r="O53">
-        <v>60.27609668112245</v>
+        <v>59.76017180612244</v>
       </c>
       <c r="P53">
-        <v>180.8282900433674</v>
+        <v>179.2805154183673</v>
       </c>
       <c r="Q53">
-        <v>267.1282900433674</v>
+        <v>265.5805154183673</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09773507984414499</v>
+        <v>0.09866514932559457</v>
       </c>
       <c r="T53">
-        <v>0.7557186927024697</v>
+        <v>0.7692523369127574</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.290806871154371</v>
+        <v>3.227522123632171</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07235827167628539</v>
+        <v>0.07230810422893975</v>
       </c>
       <c r="C54">
-        <v>1624.266858831854</v>
+        <v>1593.663642356877</v>
       </c>
       <c r="D54">
-        <v>3145.906858831854</v>
+        <v>3147.498642356877</v>
       </c>
       <c r="E54">
-        <v>-172.3599999999999</v>
+        <v>-140.165</v>
       </c>
       <c r="F54">
-        <v>1674.14</v>
+        <v>1706.335</v>
       </c>
       <c r="G54">
         <v>152.5</v>
@@ -5721,28 +5721,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M54">
-        <v>107.312374</v>
+        <v>109.3760735</v>
       </c>
       <c r="N54">
-        <v>239.0406872244898</v>
+        <v>236.9769877244898</v>
       </c>
       <c r="O54">
-        <v>59.76017180612244</v>
+        <v>59.24424693112245</v>
       </c>
       <c r="P54">
-        <v>179.2805154183673</v>
+        <v>177.7327407933673</v>
       </c>
       <c r="Q54">
-        <v>265.5805154183673</v>
+        <v>264.0327407933673</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09866514932559457</v>
+        <v>0.0996347962317867</v>
       </c>
       <c r="T54">
-        <v>0.7692523369127574</v>
+        <v>0.7833618808766746</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.227522123632171</v>
+        <v>3.166625479790055</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07230810422893975</v>
+        <v>0.0722579367815941</v>
       </c>
       <c r="C55">
-        <v>1593.663642356877</v>
+        <v>1563.062037536412</v>
       </c>
       <c r="D55">
-        <v>3147.498642356877</v>
+        <v>3149.092037536413</v>
       </c>
       <c r="E55">
-        <v>-140.165</v>
+        <v>-107.9699999999998</v>
       </c>
       <c r="F55">
-        <v>1706.335</v>
+        <v>1738.53</v>
       </c>
       <c r="G55">
         <v>152.5</v>
@@ -5803,28 +5803,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M55">
-        <v>109.3760735</v>
+        <v>111.439773</v>
       </c>
       <c r="N55">
-        <v>236.9769877244898</v>
+        <v>234.9132882244898</v>
       </c>
       <c r="O55">
-        <v>59.24424693112245</v>
+        <v>58.72832205612245</v>
       </c>
       <c r="P55">
-        <v>177.7327407933673</v>
+        <v>176.1849661683673</v>
       </c>
       <c r="Q55">
-        <v>264.0327407933673</v>
+        <v>262.4849661683674</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0996347962317867</v>
+        <v>0.1006466016991176</v>
       </c>
       <c r="T55">
-        <v>0.7833618808766746</v>
+        <v>0.7980848832738053</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.166625479790055</v>
+        <v>3.10798426720135</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0722579367815941</v>
+        <v>0.07220776933424847</v>
       </c>
       <c r="C56">
-        <v>1563.062037536412</v>
+        <v>1532.46204681936</v>
       </c>
       <c r="D56">
-        <v>3149.092037536413</v>
+        <v>3150.687046819361</v>
       </c>
       <c r="E56">
-        <v>-107.9699999999998</v>
+        <v>-75.77499999999986</v>
       </c>
       <c r="F56">
-        <v>1738.53</v>
+        <v>1770.725</v>
       </c>
       <c r="G56">
         <v>152.5</v>
@@ -5885,28 +5885,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M56">
-        <v>111.439773</v>
+        <v>113.5034725</v>
       </c>
       <c r="N56">
-        <v>234.9132882244898</v>
+        <v>232.8495887244898</v>
       </c>
       <c r="O56">
-        <v>58.72832205612245</v>
+        <v>58.21239718112245</v>
       </c>
       <c r="P56">
-        <v>176.1849661683673</v>
+        <v>174.6371915433674</v>
       </c>
       <c r="Q56">
-        <v>262.4849661683674</v>
+        <v>260.9371915433674</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1006466016991176</v>
+        <v>0.1017033762983299</v>
       </c>
       <c r="T56">
-        <v>0.7980848832738053</v>
+        <v>0.8134622413330309</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.10798426720135</v>
+        <v>3.051475462343143</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07220776933424847</v>
+        <v>0.0754336018869028</v>
       </c>
       <c r="C57">
-        <v>1532.46204681936</v>
+        <v>1400.890460173153</v>
       </c>
       <c r="D57">
-        <v>3150.687046819361</v>
+        <v>3051.310460173153</v>
       </c>
       <c r="E57">
-        <v>-75.77499999999986</v>
+        <v>-43.57999999999993</v>
       </c>
       <c r="F57">
-        <v>1770.725</v>
+        <v>1802.92</v>
       </c>
       <c r="G57">
         <v>152.5</v>
@@ -5967,45 +5967,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M57">
-        <v>113.5034725</v>
+        <v>129.629948</v>
       </c>
       <c r="N57">
-        <v>232.8495887244898</v>
+        <v>216.7231132244898</v>
       </c>
       <c r="O57">
-        <v>58.21239718112245</v>
+        <v>54.18077830612245</v>
       </c>
       <c r="P57">
-        <v>174.6371915433674</v>
+        <v>162.5423349183673</v>
       </c>
       <c r="Q57">
-        <v>260.9371915433674</v>
+        <v>248.8423349183673</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1017033762983299</v>
+        <v>0.1028081861065973</v>
       </c>
       <c r="T57">
-        <v>0.8134622413330309</v>
+        <v>0.8295385702131303</v>
       </c>
       <c r="U57">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.051475462343143</v>
+        <v>2.671859910215267</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0754336018869028</v>
+        <v>0.07544193443955716</v>
       </c>
       <c r="C58">
-        <v>1400.890460173153</v>
+        <v>1368.446880237871</v>
       </c>
       <c r="D58">
-        <v>3051.310460173153</v>
+        <v>3051.061880237872</v>
       </c>
       <c r="E58">
-        <v>-43.57999999999993</v>
+        <v>-11.38499999999976</v>
       </c>
       <c r="F58">
-        <v>1802.92</v>
+        <v>1835.115</v>
       </c>
       <c r="G58">
         <v>152.5</v>
@@ -6049,28 +6049,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M58">
-        <v>129.629948</v>
+        <v>131.9447685</v>
       </c>
       <c r="N58">
-        <v>216.7231132244898</v>
+        <v>214.4082927244898</v>
       </c>
       <c r="O58">
-        <v>54.18077830612245</v>
+        <v>53.60207318112244</v>
       </c>
       <c r="P58">
-        <v>162.5423349183673</v>
+        <v>160.8062195433673</v>
       </c>
       <c r="Q58">
-        <v>248.8423349183673</v>
+        <v>247.1062195433673</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1028081861065973</v>
+        <v>0.1039643824175748</v>
       </c>
       <c r="T58">
-        <v>0.8295385702131303</v>
+        <v>0.8463626353202112</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.671859910215267</v>
+        <v>2.624985174948332</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07544193443955716</v>
+        <v>0.07545026699221152</v>
       </c>
       <c r="C59">
-        <v>1368.446880237871</v>
+        <v>1336.003340801222</v>
       </c>
       <c r="D59">
-        <v>3051.061880237872</v>
+        <v>3050.813340801222</v>
       </c>
       <c r="E59">
-        <v>-11.38499999999976</v>
+        <v>20.81000000000017</v>
       </c>
       <c r="F59">
-        <v>1835.115</v>
+        <v>1867.31</v>
       </c>
       <c r="G59">
         <v>152.5</v>
@@ -6131,28 +6131,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M59">
-        <v>131.9447685</v>
+        <v>134.259589</v>
       </c>
       <c r="N59">
-        <v>214.4082927244898</v>
+        <v>212.0934722244898</v>
       </c>
       <c r="O59">
-        <v>53.60207318112244</v>
+        <v>53.02336805612244</v>
       </c>
       <c r="P59">
-        <v>160.8062195433673</v>
+        <v>159.0701041683673</v>
       </c>
       <c r="Q59">
-        <v>247.1062195433673</v>
+        <v>245.3701041683673</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1039643824175748</v>
+        <v>0.1051756356957417</v>
       </c>
       <c r="T59">
-        <v>0.8463626353202112</v>
+        <v>0.863987846384772</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.624985174948332</v>
+        <v>2.579726809863017</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07545026699221151</v>
+        <v>0.07545859954486586</v>
       </c>
       <c r="C60">
-        <v>1336.003340801222</v>
+        <v>1303.55984185331</v>
       </c>
       <c r="D60">
-        <v>3050.813340801222</v>
+        <v>3050.56484185331</v>
       </c>
       <c r="E60">
-        <v>20.80999999999995</v>
+        <v>53.00499999999988</v>
       </c>
       <c r="F60">
-        <v>1867.31</v>
+        <v>1899.505</v>
       </c>
       <c r="G60">
         <v>152.5</v>
@@ -6213,28 +6213,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M60">
-        <v>134.259589</v>
+        <v>136.5744095</v>
       </c>
       <c r="N60">
-        <v>212.0934722244898</v>
+        <v>209.7786517244898</v>
       </c>
       <c r="O60">
-        <v>53.02336805612245</v>
+        <v>52.44466293112245</v>
       </c>
       <c r="P60">
-        <v>159.0701041683674</v>
+        <v>157.3339887933674</v>
       </c>
       <c r="Q60">
-        <v>245.3701041683673</v>
+        <v>243.6339887933673</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1051756356957417</v>
+        <v>0.1064459744996728</v>
       </c>
       <c r="T60">
-        <v>0.8639878463847718</v>
+        <v>0.8824728238427259</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.579726809863017</v>
+        <v>2.536002626645</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07545859954486586</v>
+        <v>0.07722193209752022</v>
       </c>
       <c r="C61">
-        <v>1303.55984185331</v>
+        <v>1219.672866257613</v>
       </c>
       <c r="D61">
-        <v>3050.56484185331</v>
+        <v>2998.872866257613</v>
       </c>
       <c r="E61">
-        <v>53.00499999999988</v>
+        <v>85.19999999999982</v>
       </c>
       <c r="F61">
-        <v>1899.505</v>
+        <v>1931.7</v>
       </c>
       <c r="G61">
         <v>152.5</v>
@@ -6295,45 +6295,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M61">
-        <v>136.5744095</v>
+        <v>146.42286</v>
       </c>
       <c r="N61">
-        <v>209.7786517244898</v>
+        <v>199.9302012244898</v>
       </c>
       <c r="O61">
-        <v>52.44466293112245</v>
+        <v>49.98255030612246</v>
       </c>
       <c r="P61">
-        <v>157.3339887933674</v>
+        <v>149.9476509183674</v>
       </c>
       <c r="Q61">
-        <v>243.6339887933673</v>
+        <v>236.2476509183674</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1064459744996728</v>
+        <v>0.1077798302438005</v>
       </c>
       <c r="T61">
-        <v>0.8824728238427259</v>
+        <v>0.9018820501735777</v>
       </c>
       <c r="U61">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.536002626645</v>
+        <v>2.365430242412215</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07722193209752022</v>
+        <v>0.07725951465017458</v>
       </c>
       <c r="C62">
-        <v>1219.672866257613</v>
+        <v>1186.395196129168</v>
       </c>
       <c r="D62">
-        <v>2998.872866257613</v>
+        <v>2997.790196129168</v>
       </c>
       <c r="E62">
-        <v>85.19999999999982</v>
+        <v>117.395</v>
       </c>
       <c r="F62">
-        <v>1931.7</v>
+        <v>1963.895</v>
       </c>
       <c r="G62">
         <v>152.5</v>
@@ -6377,28 +6377,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M62">
-        <v>146.42286</v>
+        <v>148.863241</v>
       </c>
       <c r="N62">
-        <v>199.9302012244898</v>
+        <v>197.4898202244898</v>
       </c>
       <c r="O62">
-        <v>49.98255030612246</v>
+        <v>49.37245505612245</v>
       </c>
       <c r="P62">
-        <v>149.9476509183674</v>
+        <v>148.1173651683673</v>
       </c>
       <c r="Q62">
-        <v>236.2476509183674</v>
+        <v>234.4173651683673</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1077798302438005</v>
+        <v>0.1091820888466015</v>
       </c>
       <c r="T62">
-        <v>0.9018820501735777</v>
+        <v>0.9222866214444732</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.365430242412215</v>
+        <v>2.326652697454637</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07725951465017458</v>
+        <v>0.07729709720282893</v>
       </c>
       <c r="C63">
-        <v>1186.395196129168</v>
+        <v>1153.118307462044</v>
       </c>
       <c r="D63">
-        <v>2997.790196129168</v>
+        <v>2996.708307462044</v>
       </c>
       <c r="E63">
-        <v>117.395</v>
+        <v>149.5899999999999</v>
       </c>
       <c r="F63">
-        <v>1963.895</v>
+        <v>1996.09</v>
       </c>
       <c r="G63">
         <v>152.5</v>
@@ -6459,28 +6459,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M63">
-        <v>148.863241</v>
+        <v>151.303622</v>
       </c>
       <c r="N63">
-        <v>197.4898202244898</v>
+        <v>195.0494392244898</v>
       </c>
       <c r="O63">
-        <v>49.37245505612245</v>
+        <v>48.76235980612245</v>
       </c>
       <c r="P63">
-        <v>148.1173651683673</v>
+        <v>146.2870794183673</v>
       </c>
       <c r="Q63">
-        <v>234.4173651683673</v>
+        <v>232.5870794183674</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1091820888466015</v>
+        <v>0.1106581505337603</v>
       </c>
       <c r="T63">
-        <v>0.9222866214444732</v>
+        <v>0.9437651175190999</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.326652697454637</v>
+        <v>2.289126041044079</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07729709720282893</v>
+        <v>0.07733467975548328</v>
       </c>
       <c r="C64">
-        <v>1153.118307462044</v>
+        <v>1119.842199410468</v>
       </c>
       <c r="D64">
-        <v>2996.708307462044</v>
+        <v>2995.627199410468</v>
       </c>
       <c r="E64">
-        <v>149.5899999999999</v>
+        <v>181.7850000000001</v>
       </c>
       <c r="F64">
-        <v>1996.09</v>
+        <v>2028.285</v>
       </c>
       <c r="G64">
         <v>152.5</v>
@@ -6541,28 +6541,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M64">
-        <v>151.303622</v>
+        <v>153.744003</v>
       </c>
       <c r="N64">
-        <v>195.0494392244898</v>
+        <v>192.6090582244898</v>
       </c>
       <c r="O64">
-        <v>48.76235980612245</v>
+        <v>48.15226455612245</v>
       </c>
       <c r="P64">
-        <v>146.2870794183673</v>
+        <v>144.4567936683673</v>
       </c>
       <c r="Q64">
-        <v>232.5870794183674</v>
+        <v>230.7567936683673</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1106581505337603</v>
+        <v>0.112213999339144</v>
       </c>
       <c r="T64">
-        <v>0.9437651175190999</v>
+        <v>0.9664046133815444</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.289126041044079</v>
+        <v>2.252790707059252</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07733467975548328</v>
+        <v>0.07737226230813762</v>
       </c>
       <c r="C65">
-        <v>1119.842199410468</v>
+        <v>1086.566871129888</v>
       </c>
       <c r="D65">
-        <v>2995.627199410468</v>
+        <v>2994.546871129888</v>
       </c>
       <c r="E65">
-        <v>181.7850000000001</v>
+        <v>213.98</v>
       </c>
       <c r="F65">
-        <v>2028.285</v>
+        <v>2060.48</v>
       </c>
       <c r="G65">
         <v>152.5</v>
@@ -6623,28 +6623,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M65">
-        <v>153.744003</v>
+        <v>156.184384</v>
       </c>
       <c r="N65">
-        <v>192.6090582244898</v>
+        <v>190.1686772244898</v>
       </c>
       <c r="O65">
-        <v>48.15226455612245</v>
+        <v>47.54216930612245</v>
       </c>
       <c r="P65">
-        <v>144.4567936683673</v>
+        <v>142.6265079183673</v>
       </c>
       <c r="Q65">
-        <v>230.7567936683673</v>
+        <v>228.9265079183673</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.112213999339144</v>
+        <v>0.1138562841892712</v>
       </c>
       <c r="T65">
-        <v>0.9664046133815444</v>
+        <v>0.9903018590141246</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.252790707059252</v>
+        <v>2.217590852261451</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07737226230813762</v>
+        <v>0.07740984486079198</v>
       </c>
       <c r="C66">
-        <v>1086.566871129888</v>
+        <v>1053.292321776969</v>
       </c>
       <c r="D66">
-        <v>2994.546871129888</v>
+        <v>2993.467321776969</v>
       </c>
       <c r="E66">
-        <v>213.98</v>
+        <v>246.1750000000002</v>
       </c>
       <c r="F66">
-        <v>2060.48</v>
+        <v>2092.675</v>
       </c>
       <c r="G66">
         <v>152.5</v>
@@ -6705,28 +6705,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M66">
-        <v>156.184384</v>
+        <v>158.624765</v>
       </c>
       <c r="N66">
-        <v>190.1686772244898</v>
+        <v>187.7282962244898</v>
       </c>
       <c r="O66">
-        <v>47.54216930612245</v>
+        <v>46.93207405612245</v>
       </c>
       <c r="P66">
-        <v>142.6265079183673</v>
+        <v>140.7962221683673</v>
       </c>
       <c r="Q66">
-        <v>228.9265079183673</v>
+        <v>227.0962221683673</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1138562841892712</v>
+        <v>0.1155924138879771</v>
       </c>
       <c r="T66">
-        <v>0.9903018590141246</v>
+        <v>1.015564661539995</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.217590852261451</v>
+        <v>2.183474069918967</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07740984486079198</v>
+        <v>0.07744742741344633</v>
       </c>
       <c r="C67">
-        <v>1053.292321776969</v>
+        <v>1020.018550509594</v>
       </c>
       <c r="D67">
-        <v>2993.467321776969</v>
+        <v>2992.388550509594</v>
       </c>
       <c r="E67">
-        <v>246.1750000000002</v>
+        <v>278.3699999999999</v>
       </c>
       <c r="F67">
-        <v>2092.675</v>
+        <v>2124.87</v>
       </c>
       <c r="G67">
         <v>152.5</v>
@@ -6787,28 +6787,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M67">
-        <v>158.624765</v>
+        <v>161.065146</v>
       </c>
       <c r="N67">
-        <v>187.7282962244898</v>
+        <v>185.2879152244898</v>
       </c>
       <c r="O67">
-        <v>46.93207405612245</v>
+        <v>46.32197880612245</v>
       </c>
       <c r="P67">
-        <v>140.7962221683673</v>
+        <v>138.9659364183674</v>
       </c>
       <c r="Q67">
-        <v>227.0962221683673</v>
+        <v>225.2659364183673</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1155924138879771</v>
+        <v>0.1174306688630774</v>
       </c>
       <c r="T67">
-        <v>1.015564661539995</v>
+        <v>1.04231351127327</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.183474069918967</v>
+        <v>2.15039112946565</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07744742741344633</v>
+        <v>0.07748500996610068</v>
       </c>
       <c r="C68">
-        <v>1020.018550509594</v>
+        <v>986.7455564868569</v>
       </c>
       <c r="D68">
-        <v>2992.388550509594</v>
+        <v>2991.310556486857</v>
       </c>
       <c r="E68">
-        <v>278.3699999999999</v>
+        <v>310.5650000000001</v>
       </c>
       <c r="F68">
-        <v>2124.87</v>
+        <v>2157.065</v>
       </c>
       <c r="G68">
         <v>152.5</v>
@@ -6869,28 +6869,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M68">
-        <v>161.065146</v>
+        <v>163.505527</v>
       </c>
       <c r="N68">
-        <v>185.2879152244898</v>
+        <v>182.8475342244898</v>
       </c>
       <c r="O68">
-        <v>46.32197880612245</v>
+        <v>45.71188355612244</v>
       </c>
       <c r="P68">
-        <v>138.9659364183674</v>
+        <v>137.1356506683673</v>
       </c>
       <c r="Q68">
-        <v>225.2659364183673</v>
+        <v>223.4356506683673</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1174306688630774</v>
+        <v>0.1193803332306081</v>
       </c>
       <c r="T68">
-        <v>1.04231351127327</v>
+        <v>1.070683503414622</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.15039112946565</v>
+        <v>2.118295739473625</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07748500996610068</v>
+        <v>0.07752259251875504</v>
       </c>
       <c r="C69">
-        <v>986.7455564868569</v>
+        <v>953.4733388690638</v>
       </c>
       <c r="D69">
-        <v>2991.310556486857</v>
+        <v>2990.233338869064</v>
       </c>
       <c r="E69">
-        <v>310.5650000000001</v>
+        <v>342.7600000000002</v>
       </c>
       <c r="F69">
-        <v>2157.065</v>
+        <v>2189.26</v>
       </c>
       <c r="G69">
         <v>152.5</v>
@@ -6951,28 +6951,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M69">
-        <v>163.505527</v>
+        <v>165.945908</v>
       </c>
       <c r="N69">
-        <v>182.8475342244898</v>
+        <v>180.4071532244898</v>
       </c>
       <c r="O69">
-        <v>45.71188355612244</v>
+        <v>45.10178830612244</v>
       </c>
       <c r="P69">
-        <v>137.1356506683673</v>
+        <v>135.3053649183673</v>
       </c>
       <c r="Q69">
-        <v>223.4356506683673</v>
+        <v>221.6053649183673</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1193803332306081</v>
+        <v>0.1214518516211095</v>
       </c>
       <c r="T69">
-        <v>1.070683503414622</v>
+        <v>1.100826620064808</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.118295739473625</v>
+        <v>2.087144331540189</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07752259251875504</v>
+        <v>0.07756017507140939</v>
       </c>
       <c r="C70">
-        <v>953.4733388690638</v>
+        <v>920.2018968177313</v>
       </c>
       <c r="D70">
-        <v>2990.233338869064</v>
+        <v>2989.156896817732</v>
       </c>
       <c r="E70">
-        <v>342.7600000000002</v>
+        <v>374.9550000000004</v>
       </c>
       <c r="F70">
-        <v>2189.26</v>
+        <v>2221.455</v>
       </c>
       <c r="G70">
         <v>152.5</v>
@@ -7033,28 +7033,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M70">
-        <v>165.945908</v>
+        <v>168.386289</v>
       </c>
       <c r="N70">
-        <v>180.4071532244898</v>
+        <v>177.9667722244898</v>
       </c>
       <c r="O70">
-        <v>45.10178830612244</v>
+        <v>44.49169305612244</v>
       </c>
       <c r="P70">
-        <v>135.3053649183673</v>
+        <v>133.4750791683673</v>
       </c>
       <c r="Q70">
-        <v>221.6053649183673</v>
+        <v>219.7750791683673</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1214518516211095</v>
+        <v>0.1236570163593851</v>
       </c>
       <c r="T70">
-        <v>1.100826620064808</v>
+        <v>1.132914453918233</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.087144331540189</v>
+        <v>2.056895862967143</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07756017507140939</v>
+        <v>0.07759775762406373</v>
       </c>
       <c r="C71">
-        <v>920.2018968177313</v>
+        <v>886.9312294955812</v>
       </c>
       <c r="D71">
-        <v>2989.156896817732</v>
+        <v>2988.081229495581</v>
       </c>
       <c r="E71">
-        <v>374.9550000000004</v>
+        <v>407.1500000000001</v>
       </c>
       <c r="F71">
-        <v>2221.455</v>
+        <v>2253.65</v>
       </c>
       <c r="G71">
         <v>152.5</v>
@@ -7115,28 +7115,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M71">
-        <v>168.386289</v>
+        <v>170.82667</v>
       </c>
       <c r="N71">
-        <v>177.9667722244898</v>
+        <v>175.5263912244898</v>
       </c>
       <c r="O71">
-        <v>44.49169305612244</v>
+        <v>43.88159780612245</v>
       </c>
       <c r="P71">
-        <v>133.4750791683673</v>
+        <v>131.6447934183674</v>
       </c>
       <c r="Q71">
-        <v>219.7750791683673</v>
+        <v>217.9447934183673</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1236570163593851</v>
+        <v>0.1260091920802125</v>
       </c>
       <c r="T71">
-        <v>1.132914453918233</v>
+        <v>1.167141476695218</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.056895862967143</v>
+        <v>2.027511636353327</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07759775762406373</v>
+        <v>0.08519684017671809</v>
       </c>
       <c r="C72">
-        <v>886.9312294955812</v>
+        <v>652.0644865209915</v>
       </c>
       <c r="D72">
-        <v>2988.081229495581</v>
+        <v>2785.409486520992</v>
       </c>
       <c r="E72">
-        <v>407.1500000000001</v>
+        <v>439.3450000000003</v>
       </c>
       <c r="F72">
-        <v>2253.65</v>
+        <v>2285.845</v>
       </c>
       <c r="G72">
         <v>152.5</v>
@@ -7197,45 +7197,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M72">
-        <v>170.82667</v>
+        <v>205.72605</v>
       </c>
       <c r="N72">
-        <v>175.5263912244898</v>
+        <v>140.6270112244898</v>
       </c>
       <c r="O72">
-        <v>43.88159780612245</v>
+        <v>35.15675280612245</v>
       </c>
       <c r="P72">
-        <v>131.6447934183674</v>
+        <v>105.4702584183673</v>
       </c>
       <c r="Q72">
-        <v>217.9447934183673</v>
+        <v>191.7702584183673</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1260091920802125</v>
+        <v>0.1285235868162693</v>
       </c>
       <c r="T72">
-        <v>1.167141476695218</v>
+        <v>1.203728983801652</v>
       </c>
       <c r="U72">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.027511636353327</v>
+        <v>1.683564435444562</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08519684017671809</v>
+        <v>0.08534092272937245</v>
       </c>
       <c r="C73">
-        <v>652.064486520992</v>
+        <v>616.2919676917581</v>
       </c>
       <c r="D73">
-        <v>2785.409486520992</v>
+        <v>2781.831967691758</v>
       </c>
       <c r="E73">
-        <v>439.3449999999998</v>
+        <v>471.54</v>
       </c>
       <c r="F73">
-        <v>2285.845</v>
+        <v>2318.04</v>
       </c>
       <c r="G73">
         <v>152.5</v>
@@ -7279,28 +7279,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M73">
-        <v>205.72605</v>
+        <v>208.6236</v>
       </c>
       <c r="N73">
-        <v>140.6270112244898</v>
+        <v>137.7294612244898</v>
       </c>
       <c r="O73">
-        <v>35.15675280612246</v>
+        <v>34.43236530612246</v>
       </c>
       <c r="P73">
-        <v>105.4702584183674</v>
+        <v>103.2970959183674</v>
       </c>
       <c r="Q73">
-        <v>191.7702584183673</v>
+        <v>189.5970959183674</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1285235868162693</v>
+        <v>0.1312175811763301</v>
       </c>
       <c r="T73">
-        <v>1.203728983801651</v>
+        <v>1.24292988427283</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.683564435444562</v>
+        <v>1.660181596063388</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08534092272937245</v>
+        <v>0.08548500528202679</v>
       </c>
       <c r="C74">
-        <v>616.2919676917581</v>
+        <v>580.5286268479003</v>
       </c>
       <c r="D74">
-        <v>2781.831967691758</v>
+        <v>2778.2636268479</v>
       </c>
       <c r="E74">
-        <v>471.54</v>
+        <v>503.7350000000001</v>
       </c>
       <c r="F74">
-        <v>2318.04</v>
+        <v>2350.235</v>
       </c>
       <c r="G74">
         <v>152.5</v>
@@ -7361,28 +7361,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M74">
-        <v>208.6236</v>
+        <v>211.52115</v>
       </c>
       <c r="N74">
-        <v>137.7294612244898</v>
+        <v>134.8319112244898</v>
       </c>
       <c r="O74">
-        <v>34.43236530612246</v>
+        <v>33.70797780612245</v>
       </c>
       <c r="P74">
-        <v>103.2970959183674</v>
+        <v>101.1239334183674</v>
       </c>
       <c r="Q74">
-        <v>189.5970959183674</v>
+        <v>187.4239334183674</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1312175811763301</v>
+        <v>0.1341111306741733</v>
       </c>
       <c r="T74">
-        <v>1.24292988427283</v>
+        <v>1.285034555149281</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.660181596063388</v>
+        <v>1.637439382418684</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08548500528202679</v>
+        <v>0.08562908783468115</v>
       </c>
       <c r="C75">
-        <v>580.5286268479003</v>
+        <v>544.7744287160172</v>
       </c>
       <c r="D75">
-        <v>2778.2636268479</v>
+        <v>2774.704428716017</v>
       </c>
       <c r="E75">
-        <v>503.7350000000001</v>
+        <v>535.9299999999998</v>
       </c>
       <c r="F75">
-        <v>2350.235</v>
+        <v>2382.43</v>
       </c>
       <c r="G75">
         <v>152.5</v>
@@ -7443,28 +7443,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M75">
-        <v>211.52115</v>
+        <v>214.4187</v>
       </c>
       <c r="N75">
-        <v>134.8319112244898</v>
+        <v>131.9343612244898</v>
       </c>
       <c r="O75">
-        <v>33.70797780612245</v>
+        <v>32.98359030612246</v>
       </c>
       <c r="P75">
-        <v>101.1239334183674</v>
+        <v>98.95077091836737</v>
       </c>
       <c r="Q75">
-        <v>187.4239334183674</v>
+        <v>185.2507709183674</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1341111306741733</v>
+        <v>0.1372272609026198</v>
       </c>
       <c r="T75">
-        <v>1.285034555149281</v>
+        <v>1.330378046862381</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.637439382418684</v>
+        <v>1.61531182319681</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08562908783468115</v>
+        <v>0.08577317038733551</v>
       </c>
       <c r="C76">
-        <v>544.7744287160172</v>
+        <v>509.0293382032301</v>
       </c>
       <c r="D76">
-        <v>2774.704428716017</v>
+        <v>2771.15433820323</v>
       </c>
       <c r="E76">
-        <v>535.9299999999998</v>
+        <v>568.125</v>
       </c>
       <c r="F76">
-        <v>2382.43</v>
+        <v>2414.625</v>
       </c>
       <c r="G76">
         <v>152.5</v>
@@ -7525,28 +7525,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M76">
-        <v>214.4187</v>
+        <v>217.31625</v>
       </c>
       <c r="N76">
-        <v>131.9343612244898</v>
+        <v>129.0368112244898</v>
       </c>
       <c r="O76">
-        <v>32.98359030612246</v>
+        <v>32.25920280612245</v>
       </c>
       <c r="P76">
-        <v>98.95077091836737</v>
+        <v>96.77760841836735</v>
       </c>
       <c r="Q76">
-        <v>185.2507709183674</v>
+        <v>183.0776084183673</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1372272609026198</v>
+        <v>0.140592681549342</v>
       </c>
       <c r="T76">
-        <v>1.330378046862381</v>
+        <v>1.379349017912531</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.61531182319681</v>
+        <v>1.593774332220852</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08577317038733551</v>
+        <v>0.08591725293998986</v>
       </c>
       <c r="C77">
-        <v>509.0293382032301</v>
+        <v>473.2933203960297</v>
       </c>
       <c r="D77">
-        <v>2771.15433820323</v>
+        <v>2767.61332039603</v>
       </c>
       <c r="E77">
-        <v>568.125</v>
+        <v>600.3200000000002</v>
       </c>
       <c r="F77">
-        <v>2414.625</v>
+        <v>2446.82</v>
       </c>
       <c r="G77">
         <v>152.5</v>
@@ -7607,28 +7607,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M77">
-        <v>217.31625</v>
+        <v>220.2138</v>
       </c>
       <c r="N77">
-        <v>129.0368112244898</v>
+        <v>126.1392612244898</v>
       </c>
       <c r="O77">
-        <v>32.25920280612245</v>
+        <v>31.53481530612245</v>
       </c>
       <c r="P77">
-        <v>96.77760841836735</v>
+        <v>94.60444591836733</v>
       </c>
       <c r="Q77">
-        <v>183.0776084183673</v>
+        <v>180.9044459183673</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.140592681549342</v>
+        <v>0.1442385539166244</v>
       </c>
       <c r="T77">
-        <v>1.379349017912531</v>
+        <v>1.432400903216859</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.593774332220852</v>
+        <v>1.572803617323209</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08591725293998986</v>
+        <v>0.08606133549264422</v>
       </c>
       <c r="C78">
-        <v>473.2933203960297</v>
+        <v>437.5663405591313</v>
       </c>
       <c r="D78">
-        <v>2767.61332039603</v>
+        <v>2764.081340559131</v>
       </c>
       <c r="E78">
-        <v>600.3200000000002</v>
+        <v>632.5149999999999</v>
       </c>
       <c r="F78">
-        <v>2446.82</v>
+        <v>2479.015</v>
       </c>
       <c r="G78">
         <v>152.5</v>
@@ -7689,28 +7689,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M78">
-        <v>220.2138</v>
+        <v>223.11135</v>
       </c>
       <c r="N78">
-        <v>126.1392612244898</v>
+        <v>123.2417112244898</v>
       </c>
       <c r="O78">
-        <v>31.53481530612245</v>
+        <v>30.81042780612245</v>
       </c>
       <c r="P78">
-        <v>94.60444591836733</v>
+        <v>92.43128341836737</v>
       </c>
       <c r="Q78">
-        <v>180.9044459183673</v>
+        <v>178.7312834183674</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1442385539166244</v>
+        <v>0.1482014586636705</v>
       </c>
       <c r="T78">
-        <v>1.432400903216859</v>
+        <v>1.490065995938955</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.572803617323209</v>
+        <v>1.552377596319012</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08606133549264422</v>
+        <v>0.08620541804529855</v>
       </c>
       <c r="C79">
-        <v>437.5663405591313</v>
+        <v>401.848364134336</v>
       </c>
       <c r="D79">
-        <v>2764.081340559131</v>
+        <v>2760.558364134336</v>
       </c>
       <c r="E79">
-        <v>632.5149999999999</v>
+        <v>664.71</v>
       </c>
       <c r="F79">
-        <v>2479.015</v>
+        <v>2511.21</v>
       </c>
       <c r="G79">
         <v>152.5</v>
@@ -7771,28 +7771,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M79">
-        <v>223.11135</v>
+        <v>226.0089</v>
       </c>
       <c r="N79">
-        <v>123.2417112244898</v>
+        <v>120.3441612244898</v>
       </c>
       <c r="O79">
-        <v>30.81042780612245</v>
+        <v>30.08604030612246</v>
       </c>
       <c r="P79">
-        <v>92.43128341836737</v>
+        <v>90.25812091836737</v>
       </c>
       <c r="Q79">
-        <v>178.7312834183674</v>
+        <v>176.5581209183674</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1482014586636705</v>
+        <v>0.1525246274786298</v>
       </c>
       <c r="T79">
-        <v>1.490065995938955</v>
+        <v>1.552973369817604</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.552377596319012</v>
+        <v>1.532475319443127</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08620541804529855</v>
+        <v>0.08634950059795291</v>
       </c>
       <c r="C80">
-        <v>401.848364134336</v>
+        <v>366.1393567394075</v>
       </c>
       <c r="D80">
-        <v>2760.558364134336</v>
+        <v>2757.044356739408</v>
       </c>
       <c r="E80">
-        <v>664.71</v>
+        <v>696.9050000000002</v>
       </c>
       <c r="F80">
-        <v>2511.21</v>
+        <v>2543.405</v>
       </c>
       <c r="G80">
         <v>152.5</v>
@@ -7853,28 +7853,28 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M80">
-        <v>226.0089</v>
+        <v>228.90645</v>
       </c>
       <c r="N80">
-        <v>120.3441612244898</v>
+        <v>117.4466112244898</v>
       </c>
       <c r="O80">
-        <v>30.08604030612246</v>
+        <v>29.36165280612245</v>
       </c>
       <c r="P80">
-        <v>90.25812091836737</v>
+        <v>88.08495841836735</v>
       </c>
       <c r="Q80">
-        <v>176.5581209183674</v>
+        <v>174.3849584183673</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1525246274786298</v>
+        <v>0.1572595266569186</v>
       </c>
       <c r="T80">
-        <v>1.552973369817604</v>
+        <v>1.621871922160888</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.532475319443127</v>
+        <v>1.513076897678024</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08634950059795291</v>
+        <v>0.1235284117232701</v>
       </c>
       <c r="C81">
-        <v>366.1393567394075</v>
+        <v>-347.7413278142953</v>
       </c>
       <c r="D81">
-        <v>2757.044356739408</v>
+        <v>2075.358672185705</v>
       </c>
       <c r="E81">
-        <v>696.9050000000002</v>
+        <v>729.1000000000004</v>
       </c>
       <c r="F81">
-        <v>2543.405</v>
+        <v>2575.6</v>
       </c>
       <c r="G81">
         <v>152.5</v>
@@ -7935,45 +7935,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M81">
-        <v>228.90645</v>
+        <v>378.0980800000001</v>
       </c>
       <c r="N81">
-        <v>117.4466112244898</v>
+        <v>-31.74501877551029</v>
       </c>
       <c r="O81">
-        <v>29.36165280612245</v>
+        <v>-7.936254693877572</v>
       </c>
       <c r="P81">
-        <v>88.08495841836735</v>
+        <v>-23.80876408163272</v>
       </c>
       <c r="Q81">
-        <v>174.3849584183673</v>
+        <v>62.49123591836728</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1572595266569186</v>
+        <v>0.1649167678974851</v>
       </c>
       <c r="T81">
-        <v>1.621871922160888</v>
+        <v>1.733294112275816</v>
       </c>
       <c r="U81">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.25</v>
+        <v>0.2290100634896703</v>
       </c>
       <c r="W81">
-        <v>0.0675</v>
+        <v>0.1131813226797164</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.513076897678024</v>
+        <v>0.916040253958681</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1235284117232701</v>
+        <v>0.1245384117232701</v>
       </c>
       <c r="C82">
-        <v>-347.7413278142953</v>
+        <v>-393.7831768700798</v>
       </c>
       <c r="D82">
-        <v>2075.358672185705</v>
+        <v>2061.51182312992</v>
       </c>
       <c r="E82">
-        <v>729.1000000000004</v>
+        <v>761.2950000000001</v>
       </c>
       <c r="F82">
-        <v>2575.6</v>
+        <v>2607.795</v>
       </c>
       <c r="G82">
         <v>152.5</v>
@@ -8017,37 +8017,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M82">
-        <v>378.0980800000001</v>
+        <v>382.824306</v>
       </c>
       <c r="N82">
-        <v>-31.74501877551029</v>
+        <v>-36.47124477551023</v>
       </c>
       <c r="O82">
-        <v>-7.936254693877572</v>
+        <v>-9.117811193877557</v>
       </c>
       <c r="P82">
-        <v>-23.80876408163272</v>
+        <v>-27.35343358163267</v>
       </c>
       <c r="Q82">
-        <v>62.49123591836728</v>
+        <v>58.94656641836733</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1649167678974851</v>
+        <v>0.1711860714710369</v>
       </c>
       <c r="T82">
-        <v>1.733294112275816</v>
+        <v>1.82452011818507</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2290100634896703</v>
+        <v>0.2261827787552299</v>
       </c>
       <c r="W82">
-        <v>0.1131813226797164</v>
+        <v>0.1135963680787322</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.916040253958681</v>
+        <v>0.9047311150209197</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1245384117232701</v>
+        <v>0.1255484117232701</v>
       </c>
       <c r="C83">
-        <v>-393.7831768700798</v>
+        <v>-439.6414774651471</v>
       </c>
       <c r="D83">
-        <v>2061.51182312992</v>
+        <v>2047.848522534853</v>
       </c>
       <c r="E83">
-        <v>761.2950000000001</v>
+        <v>793.4900000000002</v>
       </c>
       <c r="F83">
-        <v>2607.795</v>
+        <v>2639.99</v>
       </c>
       <c r="G83">
         <v>152.5</v>
@@ -8099,37 +8099,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M83">
-        <v>382.824306</v>
+        <v>387.5505320000001</v>
       </c>
       <c r="N83">
-        <v>-36.47124477551023</v>
+        <v>-41.19747077551028</v>
       </c>
       <c r="O83">
-        <v>-9.117811193877557</v>
+        <v>-10.29936769387757</v>
       </c>
       <c r="P83">
-        <v>-27.35343358163267</v>
+        <v>-30.89810308163271</v>
       </c>
       <c r="Q83">
-        <v>58.94656641836733</v>
+        <v>55.40189691836729</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1711860714710369</v>
+        <v>0.178151964330539</v>
       </c>
       <c r="T83">
-        <v>1.82452011818507</v>
+        <v>1.925882346973129</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2261827787552299</v>
+        <v>0.2234244521850442</v>
       </c>
       <c r="W83">
-        <v>0.1135963680787322</v>
+        <v>0.1140012904192355</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9047311150209197</v>
+        <v>0.8936978087401767</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1255484117232701</v>
+        <v>0.1265584117232701</v>
       </c>
       <c r="C84">
-        <v>-439.6414774651471</v>
+        <v>-485.3198551409228</v>
       </c>
       <c r="D84">
-        <v>2047.848522534853</v>
+        <v>2034.365144859078</v>
       </c>
       <c r="E84">
-        <v>793.4900000000002</v>
+        <v>825.6850000000004</v>
       </c>
       <c r="F84">
-        <v>2639.99</v>
+        <v>2672.185</v>
       </c>
       <c r="G84">
         <v>152.5</v>
@@ -8181,37 +8181,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M84">
-        <v>387.5505320000001</v>
+        <v>392.2767580000001</v>
       </c>
       <c r="N84">
-        <v>-41.19747077551028</v>
+        <v>-45.92369677551028</v>
       </c>
       <c r="O84">
-        <v>-10.29936769387757</v>
+        <v>-11.48092419387757</v>
       </c>
       <c r="P84">
-        <v>-30.89810308163271</v>
+        <v>-34.44277258163271</v>
       </c>
       <c r="Q84">
-        <v>55.40189691836729</v>
+        <v>51.85722741836729</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.178151964330539</v>
+        <v>0.1859373739970412</v>
       </c>
       <c r="T84">
-        <v>1.925882346973129</v>
+        <v>2.039169543853901</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2234244521850442</v>
+        <v>0.2207325913153448</v>
       </c>
       <c r="W84">
-        <v>0.1140012904192355</v>
+        <v>0.1143964555949074</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8936978087401767</v>
+        <v>0.8829303652613794</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1265584117232701</v>
+        <v>0.1275684117232701</v>
       </c>
       <c r="C85">
-        <v>-485.3198551409228</v>
+        <v>-530.8218405787188</v>
       </c>
       <c r="D85">
-        <v>2034.365144859078</v>
+        <v>2021.058159421281</v>
       </c>
       <c r="E85">
-        <v>825.6850000000004</v>
+        <v>857.8800000000001</v>
       </c>
       <c r="F85">
-        <v>2672.185</v>
+        <v>2704.38</v>
       </c>
       <c r="G85">
         <v>152.5</v>
@@ -8263,37 +8263,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M85">
-        <v>392.2767580000001</v>
+        <v>397.002984</v>
       </c>
       <c r="N85">
-        <v>-45.92369677551028</v>
+        <v>-50.64992277551022</v>
       </c>
       <c r="O85">
-        <v>-11.48092419387757</v>
+        <v>-12.66248069387755</v>
       </c>
       <c r="P85">
-        <v>-34.44277258163271</v>
+        <v>-37.98744208163266</v>
       </c>
       <c r="Q85">
-        <v>51.85722741836729</v>
+        <v>48.31255791836733</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1859373739970412</v>
+        <v>0.1946959598718564</v>
       </c>
       <c r="T85">
-        <v>2.039169543853901</v>
+        <v>2.166617640344771</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2207325913153448</v>
+        <v>0.2181048223711146</v>
       </c>
       <c r="W85">
-        <v>0.1143964555949074</v>
+        <v>0.1147822120759204</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8829303652613794</v>
+        <v>0.8724192894844583</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1275684117232701</v>
+        <v>0.1285784117232701</v>
       </c>
       <c r="C86">
-        <v>-530.8218405787188</v>
+        <v>-576.1508726820216</v>
       </c>
       <c r="D86">
-        <v>2021.058159421281</v>
+        <v>2007.924127317978</v>
       </c>
       <c r="E86">
-        <v>857.8800000000001</v>
+        <v>890.0749999999998</v>
       </c>
       <c r="F86">
-        <v>2704.38</v>
+        <v>2736.575</v>
       </c>
       <c r="G86">
         <v>152.5</v>
@@ -8345,37 +8345,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M86">
-        <v>397.002984</v>
+        <v>401.72921</v>
       </c>
       <c r="N86">
-        <v>-50.64992277551022</v>
+        <v>-55.37614877551022</v>
       </c>
       <c r="O86">
-        <v>-12.66248069387755</v>
+        <v>-13.84403719387755</v>
       </c>
       <c r="P86">
-        <v>-37.98744208163266</v>
+        <v>-41.53211158163266</v>
       </c>
       <c r="Q86">
-        <v>48.31255791836733</v>
+        <v>44.76788841836733</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1946959598718563</v>
+        <v>0.2046223571966467</v>
       </c>
       <c r="T86">
-        <v>2.166617640344769</v>
+        <v>2.311058816367754</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2181048223711146</v>
+        <v>0.2155388832843956</v>
       </c>
       <c r="W86">
-        <v>0.1147822120759204</v>
+        <v>0.1151588919338507</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8724192894844583</v>
+        <v>0.8621555331375823</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1285784117232701</v>
+        <v>0.1295884117232701</v>
       </c>
       <c r="C87">
-        <v>-576.1508726820216</v>
+        <v>-621.3103015393694</v>
       </c>
       <c r="D87">
-        <v>2007.924127317978</v>
+        <v>1994.959698460631</v>
       </c>
       <c r="E87">
-        <v>890.0749999999998</v>
+        <v>922.27</v>
       </c>
       <c r="F87">
-        <v>2736.575</v>
+        <v>2768.77</v>
       </c>
       <c r="G87">
         <v>152.5</v>
@@ -8427,37 +8427,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M87">
-        <v>401.72921</v>
+        <v>406.455436</v>
       </c>
       <c r="N87">
-        <v>-55.37614877551022</v>
+        <v>-60.10237477551021</v>
       </c>
       <c r="O87">
-        <v>-13.84403719387755</v>
+        <v>-15.02559369387755</v>
       </c>
       <c r="P87">
-        <v>-41.53211158163266</v>
+        <v>-45.07678108163266</v>
       </c>
       <c r="Q87">
-        <v>44.76788841836733</v>
+        <v>41.22321891836734</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2046223571966467</v>
+        <v>0.2159668112821214</v>
       </c>
       <c r="T87">
-        <v>2.311058816367754</v>
+        <v>2.476134446108308</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2155388832843956</v>
+        <v>0.2130326171996933</v>
       </c>
       <c r="W87">
-        <v>0.1151588919338507</v>
+        <v>0.115526811795085</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8621555331375823</v>
+        <v>0.8521304687987733</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1295884117232701</v>
+        <v>0.1305984117232701</v>
       </c>
       <c r="C88">
-        <v>-621.3103015393694</v>
+        <v>-666.3033912731826</v>
       </c>
       <c r="D88">
-        <v>1994.959698460631</v>
+        <v>1982.161608726817</v>
       </c>
       <c r="E88">
-        <v>922.27</v>
+        <v>954.4650000000001</v>
       </c>
       <c r="F88">
-        <v>2768.77</v>
+        <v>2800.965</v>
       </c>
       <c r="G88">
         <v>152.5</v>
@@ -8509,37 +8509,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M88">
-        <v>406.455436</v>
+        <v>411.1816620000001</v>
       </c>
       <c r="N88">
-        <v>-60.10237477551021</v>
+        <v>-64.82860077551027</v>
       </c>
       <c r="O88">
-        <v>-15.02559369387755</v>
+        <v>-16.20715019387757</v>
       </c>
       <c r="P88">
-        <v>-45.07678108163266</v>
+        <v>-48.6214505816327</v>
       </c>
       <c r="Q88">
-        <v>41.22321891836734</v>
+        <v>37.6785494183673</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2159668112821214</v>
+        <v>0.2290565659961308</v>
       </c>
       <c r="T88">
-        <v>2.476134446108308</v>
+        <v>2.666606326578178</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2130326171996933</v>
+        <v>0.210583966427283</v>
       </c>
       <c r="W88">
-        <v>0.115526811795085</v>
+        <v>0.1158862737284749</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8521304687987733</v>
+        <v>0.8423358657091321</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1305984117232701</v>
+        <v>0.1316084117232701</v>
       </c>
       <c r="C89">
-        <v>-666.3033912731826</v>
+        <v>-711.1333227796458</v>
       </c>
       <c r="D89">
-        <v>1982.161608726817</v>
+        <v>1969.526677220354</v>
       </c>
       <c r="E89">
-        <v>954.4650000000001</v>
+        <v>986.6599999999999</v>
       </c>
       <c r="F89">
-        <v>2800.965</v>
+        <v>2833.16</v>
       </c>
       <c r="G89">
         <v>152.5</v>
@@ -8591,37 +8591,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M89">
-        <v>411.1816620000001</v>
+        <v>415.907888</v>
       </c>
       <c r="N89">
-        <v>-64.82860077551027</v>
+        <v>-69.55482677551021</v>
       </c>
       <c r="O89">
-        <v>-16.20715019387757</v>
+        <v>-17.38870669387755</v>
       </c>
       <c r="P89">
-        <v>-48.6214505816327</v>
+        <v>-52.16612008163266</v>
       </c>
       <c r="Q89">
-        <v>37.6785494183673</v>
+        <v>34.13387991836734</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2290565659961308</v>
+        <v>0.2443279464958084</v>
       </c>
       <c r="T89">
-        <v>2.666606326578178</v>
+        <v>2.888823520459693</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.210583966427283</v>
+        <v>0.2081909668087912</v>
       </c>
       <c r="W89">
-        <v>0.1158862737284749</v>
+        <v>0.1162375660724695</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8423358657091321</v>
+        <v>0.8327638672351648</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1316084117232701</v>
+        <v>0.1326184117232701</v>
       </c>
       <c r="C90">
-        <v>-711.1333227796458</v>
+        <v>-755.8031963644585</v>
       </c>
       <c r="D90">
-        <v>1969.526677220354</v>
+        <v>1957.051803635542</v>
       </c>
       <c r="E90">
-        <v>986.6599999999999</v>
+        <v>1018.855</v>
       </c>
       <c r="F90">
-        <v>2833.16</v>
+        <v>2865.355</v>
       </c>
       <c r="G90">
         <v>152.5</v>
@@ -8673,37 +8673,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M90">
-        <v>415.907888</v>
+        <v>420.6341140000001</v>
       </c>
       <c r="N90">
-        <v>-69.55482677551021</v>
+        <v>-74.28105277551026</v>
       </c>
       <c r="O90">
-        <v>-17.38870669387755</v>
+        <v>-18.57026319387757</v>
       </c>
       <c r="P90">
-        <v>-52.16612008163266</v>
+        <v>-55.7107895816327</v>
       </c>
       <c r="Q90">
-        <v>34.13387991836734</v>
+        <v>30.5892104183673</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2443279464958084</v>
+        <v>0.262375941631791</v>
       </c>
       <c r="T90">
-        <v>2.888823520459693</v>
+        <v>3.151443840501484</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2081909668087912</v>
+        <v>0.205851742462625</v>
       </c>
       <c r="W90">
-        <v>0.1162375660724695</v>
+        <v>0.1165809642064867</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8327638672351648</v>
+        <v>0.8234069698505</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1326184117232701</v>
+        <v>0.1336284117232701</v>
       </c>
       <c r="C91">
-        <v>-755.8031963644585</v>
+        <v>-800.3160342790479</v>
       </c>
       <c r="D91">
-        <v>1957.051803635542</v>
+        <v>1944.733965720952</v>
       </c>
       <c r="E91">
-        <v>1018.855</v>
+        <v>1051.05</v>
       </c>
       <c r="F91">
-        <v>2865.355</v>
+        <v>2897.55</v>
       </c>
       <c r="G91">
         <v>152.5</v>
@@ -8755,37 +8755,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M91">
-        <v>420.6341140000001</v>
+        <v>425.3603400000001</v>
       </c>
       <c r="N91">
-        <v>-74.28105277551026</v>
+        <v>-79.00727877551026</v>
       </c>
       <c r="O91">
-        <v>-18.57026319387757</v>
+        <v>-19.75181969387756</v>
       </c>
       <c r="P91">
-        <v>-55.7107895816327</v>
+        <v>-59.25545908163269</v>
       </c>
       <c r="Q91">
-        <v>30.5892104183673</v>
+        <v>27.0445409183673</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.262375941631791</v>
+        <v>0.2840335357949701</v>
       </c>
       <c r="T91">
-        <v>3.151443840501484</v>
+        <v>3.466588224551632</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.205851742462625</v>
+        <v>0.2035645008797069</v>
       </c>
       <c r="W91">
-        <v>0.1165809642064867</v>
+        <v>0.116916731270859</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8234069698505</v>
+        <v>0.8142580035188277</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1336284117232701</v>
+        <v>0.1346384117232701</v>
       </c>
       <c r="C92">
-        <v>-800.3160342790479</v>
+        <v>-844.6747831616044</v>
       </c>
       <c r="D92">
-        <v>1944.733965720952</v>
+        <v>1932.570216838395</v>
       </c>
       <c r="E92">
-        <v>1051.05</v>
+        <v>1083.245</v>
       </c>
       <c r="F92">
-        <v>2897.55</v>
+        <v>2929.745</v>
       </c>
       <c r="G92">
         <v>152.5</v>
@@ -8837,37 +8837,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M92">
-        <v>425.3603400000001</v>
+        <v>430.086566</v>
       </c>
       <c r="N92">
-        <v>-79.00727877551026</v>
+        <v>-83.7335047755102</v>
       </c>
       <c r="O92">
-        <v>-19.75181969387756</v>
+        <v>-20.93337619387755</v>
       </c>
       <c r="P92">
-        <v>-59.25545908163269</v>
+        <v>-62.80012858163265</v>
       </c>
       <c r="Q92">
-        <v>27.0445409183673</v>
+        <v>23.49987141836735</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2840335357949701</v>
+        <v>0.3105039286610779</v>
       </c>
       <c r="T92">
-        <v>3.466588224551632</v>
+        <v>3.851764693946258</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2035645008797069</v>
+        <v>0.2013275283425673</v>
       </c>
       <c r="W92">
-        <v>0.116916731270859</v>
+        <v>0.1172451188393111</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8142580035188277</v>
+        <v>0.8053101133702693</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1346384117232701</v>
+        <v>0.18676544244724</v>
       </c>
       <c r="C93">
-        <v>-844.6747831616044</v>
+        <v>-1348.48326739411</v>
       </c>
       <c r="D93">
-        <v>1932.570216838395</v>
+        <v>1460.95673260589</v>
       </c>
       <c r="E93">
-        <v>1083.245</v>
+        <v>1115.44</v>
       </c>
       <c r="F93">
-        <v>2929.745</v>
+        <v>2961.94</v>
       </c>
       <c r="G93">
         <v>152.5</v>
@@ -8919,45 +8919,45 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M93">
-        <v>430.086566</v>
+        <v>594.757552</v>
       </c>
       <c r="N93">
-        <v>-83.7335047755102</v>
+        <v>-248.4044907755102</v>
       </c>
       <c r="O93">
-        <v>-20.93337619387755</v>
+        <v>-62.10112269387756</v>
       </c>
       <c r="P93">
-        <v>-62.80012858163265</v>
+        <v>-186.3033680816327</v>
       </c>
       <c r="Q93">
-        <v>23.49987141836735</v>
+        <v>-100.0033680816327</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3105039286610779</v>
+        <v>0.3615548037933363</v>
       </c>
       <c r="T93">
-        <v>3.851764693946258</v>
+        <v>4.594617130720103</v>
       </c>
       <c r="U93">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.2013275283425673</v>
+        <v>0.145585818986158</v>
       </c>
       <c r="W93">
-        <v>0.1172451188393111</v>
+        <v>0.1715663675475795</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8053101133702693</v>
+        <v>0.582343275944632</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.18676544244724</v>
+        <v>0.18831544244724</v>
       </c>
       <c r="C94">
-        <v>-1348.48326739411</v>
+        <v>-1391.203143020892</v>
       </c>
       <c r="D94">
-        <v>1460.95673260589</v>
+        <v>1450.431856979108</v>
       </c>
       <c r="E94">
-        <v>1115.44</v>
+        <v>1147.635</v>
       </c>
       <c r="F94">
-        <v>2961.94</v>
+        <v>2994.135</v>
       </c>
       <c r="G94">
         <v>152.5</v>
@@ -9001,37 +9001,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M94">
-        <v>594.757552</v>
+        <v>601.2223080000001</v>
       </c>
       <c r="N94">
-        <v>-248.4044907755102</v>
+        <v>-254.8692467755103</v>
       </c>
       <c r="O94">
-        <v>-62.10112269387756</v>
+        <v>-63.71731169387758</v>
       </c>
       <c r="P94">
-        <v>-186.3033680816327</v>
+        <v>-191.1519350816327</v>
       </c>
       <c r="Q94">
-        <v>-100.0033680816327</v>
+        <v>-104.8519350816327</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3615548037933363</v>
+        <v>0.40666263290667</v>
       </c>
       <c r="T94">
-        <v>4.594617130720103</v>
+        <v>5.25099100653726</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.145585818986158</v>
+        <v>0.1440203800723283</v>
       </c>
       <c r="W94">
-        <v>0.1715663675475795</v>
+        <v>0.1718807076814765</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.582343275944632</v>
+        <v>0.5760815202893133</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.18831544244724</v>
+        <v>0.18986544244724</v>
       </c>
       <c r="C95">
-        <v>-1391.203143020892</v>
+        <v>-1433.77245882234</v>
       </c>
       <c r="D95">
-        <v>1450.431856979108</v>
+        <v>1440.05754117766</v>
       </c>
       <c r="E95">
-        <v>1147.635</v>
+        <v>1179.83</v>
       </c>
       <c r="F95">
-        <v>2994.135</v>
+        <v>3026.33</v>
       </c>
       <c r="G95">
         <v>152.5</v>
@@ -9083,37 +9083,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M95">
-        <v>601.2223080000001</v>
+        <v>607.6870640000001</v>
       </c>
       <c r="N95">
-        <v>-254.8692467755103</v>
+        <v>-261.3340027755103</v>
       </c>
       <c r="O95">
-        <v>-63.71731169387758</v>
+        <v>-65.33350069387757</v>
       </c>
       <c r="P95">
-        <v>-191.1519350816327</v>
+        <v>-196.0005020816327</v>
       </c>
       <c r="Q95">
-        <v>-104.8519350816327</v>
+        <v>-109.7005020816327</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.40666263290667</v>
+        <v>0.4668064050577818</v>
       </c>
       <c r="T95">
-        <v>5.25099100653726</v>
+        <v>6.126156174293472</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1440203800723283</v>
+        <v>0.1424882483694312</v>
       </c>
       <c r="W95">
-        <v>0.1718807076814765</v>
+        <v>0.1721883597274182</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5760815202893133</v>
+        <v>0.5699529934777248</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.18986544244724</v>
+        <v>0.19141544244724</v>
       </c>
       <c r="C96">
-        <v>-1433.77245882234</v>
+        <v>-1476.194422524168</v>
       </c>
       <c r="D96">
-        <v>1440.05754117766</v>
+        <v>1429.830577475832</v>
       </c>
       <c r="E96">
-        <v>1179.83</v>
+        <v>1212.025</v>
       </c>
       <c r="F96">
-        <v>3026.33</v>
+        <v>3058.525</v>
       </c>
       <c r="G96">
         <v>152.5</v>
@@ -9165,37 +9165,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M96">
-        <v>607.6870640000001</v>
+        <v>614.15182</v>
       </c>
       <c r="N96">
-        <v>-261.3340027755103</v>
+        <v>-267.7987587755102</v>
       </c>
       <c r="O96">
-        <v>-65.33350069387757</v>
+        <v>-66.94968969387756</v>
       </c>
       <c r="P96">
-        <v>-196.0005020816327</v>
+        <v>-200.8490690816327</v>
       </c>
       <c r="Q96">
-        <v>-109.7005020816327</v>
+        <v>-114.5490690816327</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4668064050577818</v>
+        <v>0.5510076860693384</v>
       </c>
       <c r="T96">
-        <v>6.126156174293472</v>
+        <v>7.351387409152171</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1424882483694312</v>
+        <v>0.1409883720708056</v>
       </c>
       <c r="W96">
-        <v>0.1721883597274182</v>
+        <v>0.1724895348881822</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5699529934777248</v>
+        <v>0.5639534882832224</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.19141544244724</v>
+        <v>0.19296544244724</v>
       </c>
       <c r="C97">
-        <v>-1476.194422524168</v>
+        <v>-1518.472151372481</v>
       </c>
       <c r="D97">
-        <v>1429.830577475832</v>
+        <v>1419.747848627519</v>
       </c>
       <c r="E97">
-        <v>1212.025</v>
+        <v>1244.22</v>
       </c>
       <c r="F97">
-        <v>3058.525</v>
+        <v>3090.72</v>
       </c>
       <c r="G97">
         <v>152.5</v>
@@ -9247,37 +9247,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M97">
-        <v>614.15182</v>
+        <v>620.6165760000001</v>
       </c>
       <c r="N97">
-        <v>-267.7987587755102</v>
+        <v>-274.2635147755103</v>
       </c>
       <c r="O97">
-        <v>-66.94968969387756</v>
+        <v>-68.56587869387758</v>
       </c>
       <c r="P97">
-        <v>-200.8490690816327</v>
+        <v>-205.6976360816327</v>
       </c>
       <c r="Q97">
-        <v>-114.5490690816327</v>
+        <v>-119.3976360816327</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5510076860693384</v>
+        <v>0.6773096075866732</v>
       </c>
       <c r="T97">
-        <v>7.351387409152171</v>
+        <v>9.189234261440216</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1409883720708056</v>
+        <v>0.139519743195068</v>
       </c>
       <c r="W97">
-        <v>0.1724895348881822</v>
+        <v>0.1727844355664303</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5639534882832224</v>
+        <v>0.5580789727802722</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.19296544244724</v>
+        <v>0.19451544244724</v>
       </c>
       <c r="C98">
-        <v>-1518.472151372481</v>
+        <v>-1560.608675301606</v>
       </c>
       <c r="D98">
-        <v>1419.747848627519</v>
+        <v>1409.806324698394</v>
       </c>
       <c r="E98">
-        <v>1244.22</v>
+        <v>1276.415</v>
       </c>
       <c r="F98">
-        <v>3090.72</v>
+        <v>3122.915</v>
       </c>
       <c r="G98">
         <v>152.5</v>
@@ -9329,37 +9329,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M98">
-        <v>620.616576</v>
+        <v>627.081332</v>
       </c>
       <c r="N98">
-        <v>-274.2635147755102</v>
+        <v>-280.7282707755102</v>
       </c>
       <c r="O98">
-        <v>-68.56587869387755</v>
+        <v>-70.18206769387754</v>
       </c>
       <c r="P98">
-        <v>-205.6976360816327</v>
+        <v>-210.5462030816326</v>
       </c>
       <c r="Q98">
-        <v>-119.3976360816327</v>
+        <v>-124.2462030816326</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6773096075866715</v>
+        <v>0.8878128101155622</v>
       </c>
       <c r="T98">
-        <v>9.189234261440191</v>
+        <v>12.25231234858692</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1395197431950681</v>
+        <v>0.1380813953270777</v>
       </c>
       <c r="W98">
-        <v>0.1727844355664303</v>
+        <v>0.1730732558183228</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5580789727802723</v>
+        <v>0.5523255813083108</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.19451544244724</v>
+        <v>0.19606544244724</v>
       </c>
       <c r="C99">
-        <v>-1560.608675301606</v>
+        <v>-1602.606939969761</v>
       </c>
       <c r="D99">
-        <v>1409.806324698394</v>
+        <v>1400.003060030239</v>
       </c>
       <c r="E99">
-        <v>1276.415</v>
+        <v>1308.61</v>
       </c>
       <c r="F99">
-        <v>3122.915</v>
+        <v>3155.11</v>
       </c>
       <c r="G99">
         <v>152.5</v>
@@ -9411,37 +9411,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M99">
-        <v>627.081332</v>
+        <v>633.5460880000001</v>
       </c>
       <c r="N99">
-        <v>-280.7282707755102</v>
+        <v>-287.1930267755102</v>
       </c>
       <c r="O99">
-        <v>-70.18206769387754</v>
+        <v>-71.79825669387756</v>
       </c>
       <c r="P99">
-        <v>-210.5462030816326</v>
+        <v>-215.3947700816327</v>
       </c>
       <c r="Q99">
-        <v>-124.2462030816326</v>
+        <v>-129.0947700816327</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8878128101155622</v>
+        <v>1.308819215173343</v>
       </c>
       <c r="T99">
-        <v>12.25231234858692</v>
+        <v>18.37846852288038</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1380813953270777</v>
+        <v>0.1366724014972095</v>
       </c>
       <c r="W99">
-        <v>0.1730732558183228</v>
+        <v>0.1733561817793604</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5523255813083108</v>
+        <v>0.5466896059888382</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.19606544244724</v>
+        <v>0.19761544244724</v>
       </c>
       <c r="C100">
-        <v>-1602.606939969761</v>
+        <v>-1644.469809668941</v>
       </c>
       <c r="D100">
-        <v>1400.003060030239</v>
+        <v>1390.335190331059</v>
       </c>
       <c r="E100">
-        <v>1308.61</v>
+        <v>1340.805</v>
       </c>
       <c r="F100">
-        <v>3155.11</v>
+        <v>3187.305</v>
       </c>
       <c r="G100">
         <v>152.5</v>
@@ -9493,37 +9493,37 @@
         <v>346.3530612244898</v>
       </c>
       <c r="M100">
-        <v>633.5460880000001</v>
+        <v>640.010844</v>
       </c>
       <c r="N100">
-        <v>-287.1930267755102</v>
+        <v>-293.6577827755102</v>
       </c>
       <c r="O100">
-        <v>-71.79825669387756</v>
+        <v>-73.41444569387755</v>
       </c>
       <c r="P100">
-        <v>-215.3947700816327</v>
+        <v>-220.2433370816327</v>
       </c>
       <c r="Q100">
-        <v>-129.0947700816327</v>
+        <v>-133.9433370816326</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.308819215173343</v>
+        <v>2.571838430346686</v>
       </c>
       <c r="T100">
-        <v>18.37846852288038</v>
+        <v>36.75693704576076</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1366724014972095</v>
+        <v>0.1352918721891569</v>
       </c>
       <c r="W100">
-        <v>0.1733561817793604</v>
+        <v>0.1736333920644173</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5466896059888382</v>
+        <v>0.5411674887566277</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.19761544244724</v>
-      </c>
-      <c r="C101">
-        <v>-1644.469809668941</v>
-      </c>
-      <c r="D101">
-        <v>1390.335190331059</v>
-      </c>
-      <c r="E101">
-        <v>1340.805</v>
-      </c>
-      <c r="F101">
-        <v>3187.305</v>
-      </c>
-      <c r="G101">
-        <v>152.5</v>
-      </c>
-      <c r="H101">
-        <v>1373</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>432.6530612244898</v>
-      </c>
-      <c r="K101">
-        <v>86.3</v>
-      </c>
-      <c r="L101">
-        <v>346.3530612244898</v>
-      </c>
-      <c r="M101">
-        <v>640.010844</v>
-      </c>
-      <c r="N101">
-        <v>-293.6577827755102</v>
-      </c>
-      <c r="O101">
-        <v>-73.41444569387755</v>
-      </c>
-      <c r="P101">
-        <v>-220.2433370816327</v>
-      </c>
-      <c r="Q101">
-        <v>-133.9433370816326</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.571838430346686</v>
-      </c>
-      <c r="T101">
-        <v>36.75693704576076</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1352918721891569</v>
-      </c>
-      <c r="W101">
-        <v>0.1736333920644173</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5411674887566277</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
